--- a/Thread_Certified_Products_All.xlsx
+++ b/Thread_Certified_Products_All.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charts &amp; Analysis" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="All Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Company Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Charts &amp; Analysis" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Products'!$A$4:$G$451</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Company Summary'!$A$3:$E$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Products'!$A$4:$G$452</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Company Summary'!$A$3:$E$132</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -242,14 +242,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -273,7 +273,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -301,8 +301,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -328,8 +328,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -355,14 +355,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -386,7 +386,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -414,8 +414,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -441,8 +441,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -468,14 +468,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -499,7 +499,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -527,8 +527,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -554,8 +554,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -581,14 +581,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -611,7 +611,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -639,7 +639,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
@@ -654,9 +654,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -676,9 +676,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -698,9 +698,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -720,9 +720,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1020,7 +1020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G451"/>
+  <dimension ref="A1:G452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1042,7 +1042,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: threadgroup.org/Certified-Products  |  Total: 447 products  |  Updated: 2026-06-28</t>
+          <t>Source: threadgroup.org/Certified-Products  |  Total: 448 products  |  Updated: 2026-07-04</t>
         </is>
       </c>
     </row>
@@ -4345,12 +4345,12 @@
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>Guangdong A-OK Technology Grand Development Co.,Ltd.</t>
+          <t>Grimsholm Products AB</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>Curtain motor</t>
+          <t>Smart Irrigation Valve</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
@@ -4360,12 +4360,12 @@
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>Curtain</t>
+          <t>Irrigation</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr"/>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Pergola Controller (AC296)</t>
+          <t>Curtain motor</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
@@ -4391,12 +4391,12 @@
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Curtain</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr"/>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>Pergola Controller (AC297)</t>
+          <t>Pergola Controller (AC296)</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>Roller Shades DC Motor</t>
+          <t>Pergola Controller (AC297)</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>Curtain</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr"/>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>Roller Shades Motor</t>
+          <t>Roller Shades DC Motor</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="F114" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Curtain</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr"/>
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>HUZHOU DOORMA INTEL TECH CO LTD</t>
+          <t>Guangdong A-OK Technology Grand Development Co.,Ltd.</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>25mm tubular Motor</t>
+          <t>Roller Shades Motor</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>Curtain</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr"/>
@@ -4531,12 +4531,12 @@
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>Hager group</t>
+          <t>HUZHOU DOORMA INTEL TECH CO LTD</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>Berker Application Module</t>
+          <t>25mm tubular Motor</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Curtain</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr"/>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>Berker Application module PIR</t>
+          <t>Berker Application Module</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>Presence</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr"/>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>Berker Surface mounted push button</t>
+          <t>Berker Application module PIR</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Presence</t>
         </is>
       </c>
       <c r="G118" s="7" t="inlineStr"/>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>Rotary dimmer, connectable</t>
+          <t>Berker Surface mounted push button</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>Hinkley Lighting Inc.</t>
+          <t>Hager group</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>Thread Fan Light controller</t>
+          <t>Rotary dimmer, connectable</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr"/>
@@ -4686,27 +4686,27 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>HooRii Technology Co., Ltd</t>
+          <t>Hinkley Lighting Inc.</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>HAT31</t>
+          <t>Thread Fan Light controller</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr"/>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>HCS52</t>
+          <t>HAT31</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
@@ -4753,22 +4753,22 @@
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>Hoo Max</t>
+          <t>HCS52</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>Gateway</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr"/>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>HooRii Contact Sensor 02</t>
+          <t>Hoo Max</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Gateway</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr"/>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>HooRii Energy Metering Plug (1-socket)</t>
+          <t>HooRii Contact Sensor 02</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>Smart plug</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr"/>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>HooRii Energy Metering Plug (2-socket)</t>
+          <t>HooRii Energy Metering Plug (1-socket)</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>HooRii Energy Metering Plug (3-socket)</t>
+          <t>HooRii Energy Metering Plug (2-socket)</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>HooRii Energy Metering Plug (4-socket)</t>
+          <t>HooRii Energy Metering Plug (3-socket)</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>HooRii Energy Metering Plug (5-socket)</t>
+          <t>HooRii Energy Metering Plug (4-socket)</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>HooRii Light</t>
+          <t>HooRii Energy Metering Plug (5-socket)</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
@@ -4980,12 +4980,12 @@
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Smart plug</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr"/>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>HooRii Light (Candle lamp)</t>
+          <t>HooRii Light</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>HooRii Light (Ceiling light)</t>
+          <t>HooRii Light (Candle lamp)</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>HooRii Light (Filament lamp)</t>
+          <t>HooRii Light (Ceiling light)</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>HooRii Light (LED strip)</t>
+          <t>HooRii Light (Filament lamp)</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="F134" s="6" t="inlineStr">
         <is>
-          <t>Lightstrip</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr"/>
@@ -5125,7 +5125,7 @@
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>HooRii Light (Magnetic light fixture)</t>
+          <t>HooRii Light (LED strip)</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Lightstrip</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr"/>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>HooRii Light (Panel light)</t>
+          <t>HooRii Light (Magnetic light fixture)</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>HooRii Light (Pendant light)</t>
+          <t>HooRii Light (Panel light)</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t>HooRii Light (Recessed light)</t>
+          <t>HooRii Light (Pendant light)</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>HooRii Light (Spherical bulb)</t>
+          <t>HooRii Light (Recessed light)</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>Bulb</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr"/>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>HooRii Light (Spotlight)</t>
+          <t>HooRii Light (Spherical bulb)</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="F140" s="6" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Bulb</t>
         </is>
       </c>
       <c r="G140" s="7" t="inlineStr"/>
@@ -5306,12 +5306,12 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>IKEA of Sweden AB</t>
+          <t>HooRii Technology Co., Ltd</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>ALPSTUGA air quality monitor</t>
+          <t>HooRii Light (Spotlight)</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr"/>
@@ -5342,7 +5342,7 @@
       </c>
       <c r="C142" s="7" t="inlineStr">
         <is>
-          <t>BILRESA dual button</t>
+          <t>ALPSTUGA air quality monitor</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F142" s="6" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="G142" s="7" t="inlineStr"/>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>BILRESA scroll wheel</t>
+          <t>BILRESA dual button</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>DUBBELKISEL</t>
+          <t>BILRESA scroll wheel</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
@@ -5414,12 +5414,12 @@
       </c>
       <c r="E144" s="6" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="F144" s="6" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G144" s="7" t="inlineStr"/>
@@ -5435,7 +5435,7 @@
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>GRILLPLATS plug</t>
+          <t>DUBBELKISEL</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>Smart plug</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr"/>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="C146" s="7" t="inlineStr">
         <is>
-          <t>KAJPLATS E12 CWS globe 800lm</t>
+          <t>GRILLPLATS plug</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="E146" s="6" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr">
         <is>
-          <t>Bulb</t>
+          <t>Smart plug</t>
         </is>
       </c>
       <c r="G146" s="7" t="inlineStr"/>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>KAJPLATS E14 CWS globe 806lm</t>
+          <t>KAJPLATS E12 CWS globe 800lm</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="C148" s="7" t="inlineStr">
         <is>
-          <t>KAJPLATS E26 CWS globe 1100lm</t>
+          <t>KAJPLATS E14 CWS globe 806lm</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>KAJPLATS E27 CWS globe 1055lm</t>
+          <t>KAJPLATS E26 CWS globe 1100lm</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="C150" s="7" t="inlineStr">
         <is>
-          <t>KAJPLATS GU10 CWS 575lm</t>
+          <t>KAJPLATS E27 CWS globe 1055lm</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="C152" s="7" t="inlineStr">
         <is>
-          <t>KAJPLATS WS</t>
+          <t>KAJPLATS GU10 CWS 575lm</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>Bulb, Light</t>
+          <t>Bulb</t>
         </is>
       </c>
       <c r="G152" s="7" t="inlineStr"/>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="C154" s="7" t="inlineStr">
         <is>
-          <t>KLIPPBOK water leak sensor</t>
+          <t>KAJPLATS WS</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="E154" s="6" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Bulb, Light</t>
         </is>
       </c>
       <c r="G154" s="7" t="inlineStr"/>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>MYGGBETT door/window sensor</t>
+          <t>KLIPPBOK water leak sensor</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr"/>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="C156" s="7" t="inlineStr">
         <is>
-          <t>MYGGSPRAY wrlss mtn sensor</t>
+          <t>MYGGBETT door/window sensor</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>Presence</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="G156" s="7" t="inlineStr"/>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>TIMMERFLOTTE temp/hmd sensor</t>
+          <t>MYGGSPRAY wrlss mtn sensor</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>Presence</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr"/>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C158" s="7" t="inlineStr">
         <is>
-          <t>TOFSMYGGA plug</t>
+          <t>TIMMERFLOTTE temp/hmd sensor</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr">
@@ -5848,12 +5848,12 @@
       </c>
       <c r="E158" s="6" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>Smart plug</t>
+          <t>Temperature</t>
         </is>
       </c>
       <c r="G158" s="7" t="inlineStr"/>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>TOFSMYGGA plug outdoor</t>
+          <t>TOFSMYGGA plug</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C160" s="7" t="inlineStr">
         <is>
-          <t>VARMBLIXT table/wall lamp</t>
+          <t>TOFSMYGGA plug outdoor</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="E160" s="6" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Smart plug</t>
         </is>
       </c>
       <c r="G160" s="7" t="inlineStr"/>
@@ -5926,12 +5926,12 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>ITIUS GmbH</t>
+          <t>IKEA of Sweden AB</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>ITIUS E27 RGB+CCT</t>
+          <t>VARMBLIXT table/wall lamp</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>Bulb</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr"/>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="C162" s="7" t="inlineStr">
         <is>
-          <t>ITIUS Lights (GU10)</t>
+          <t>ITIUS E27 RGB+CCT</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
@@ -5988,27 +5988,27 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>Infineon Technologies Americas Corp.</t>
+          <t>ITIUS GmbH</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>CYW30739</t>
+          <t>ITIUS Lights (GU10)</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bulb</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr"/>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="C164" s="7" t="inlineStr">
         <is>
-          <t>CYW30739B2-P5x</t>
+          <t>CYW30739</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="E164" s="6" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="F164" s="6" t="inlineStr">
@@ -6050,27 +6050,27 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>Inovelli Labs Corporation</t>
+          <t>Infineon Technologies Americas Corp.</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>White Series Smart 2-1 Switch</t>
+          <t>CYW30739B2-P5x</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr"/>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="C166" s="7" t="inlineStr">
         <is>
-          <t>White Series Smart Fan Switch</t>
+          <t>White Series Smart 2-1 Switch</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="E166" s="6" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F166" s="6" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>White Series Smart Fan/Light Canopy Module</t>
+          <t>White Series Smart Fan Switch</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr"/>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C168" s="7" t="inlineStr">
         <is>
-          <t>White Series Smart On/Off Switch</t>
+          <t>White Series Smart Fan/Light Canopy Module</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="G168" s="7" t="inlineStr"/>
@@ -6174,12 +6174,12 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>Insta GmbH</t>
+          <t>Inovelli Labs Corporation</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>Insta Push Button Module</t>
+          <t>White Series Smart On/Off Switch</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="B170" s="7" t="inlineStr">
         <is>
-          <t>Inventronics GmbH</t>
+          <t>Insta GmbH</t>
         </is>
       </c>
       <c r="C170" s="7" t="inlineStr">
         <is>
-          <t>D+ D4i BR LI</t>
+          <t>Insta Push Button Module</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
@@ -6220,12 +6220,12 @@
       </c>
       <c r="E170" s="6" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G170" s="7" t="inlineStr"/>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>D+ D4i BR LS/PD LI O</t>
+          <t>D+ D4i BR LI</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="C172" s="7" t="inlineStr">
         <is>
-          <t>OT Wi 35/220 - 240/400 D NFC DALI+ L</t>
+          <t>D+ D4i BR LS/PD LI O</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G172" s="7" t="inlineStr"/>
@@ -6298,12 +6298,12 @@
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>KASTA Technologies (AU) Pty LTD</t>
+          <t>Inventronics GmbH</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>Kasta Matter Dimmer</t>
+          <t>OT Wi 35/220 - 240/400 D NFC DALI+ L</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr"/>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="C174" s="7" t="inlineStr">
         <is>
-          <t>Kasta Matter Relay</t>
+          <t>Kasta Matter Dimmer</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>Kasta Matter Remote</t>
+          <t>Kasta Matter Relay</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="B176" s="7" t="inlineStr">
         <is>
-          <t>LEEDARSON IoT Technology Inc</t>
+          <t>KASTA Technologies (AU) Pty LTD</t>
         </is>
       </c>
       <c r="C176" s="7" t="inlineStr">
         <is>
-          <t>A19 Smart RGB LED Bulb</t>
+          <t>Kasta Matter Remote</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
@@ -6406,12 +6406,12 @@
       </c>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>Bulb</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G176" s="7" t="inlineStr"/>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>Smart Plug</t>
+          <t>A19 Smart RGB LED Bulb</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>Smart plug</t>
+          <t>Bulb</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr"/>
@@ -6453,12 +6453,12 @@
       </c>
       <c r="B178" s="7" t="inlineStr">
         <is>
-          <t>LG Electronics</t>
+          <t>LEEDARSON IoT Technology Inc</t>
         </is>
       </c>
       <c r="C178" s="7" t="inlineStr">
         <is>
-          <t>LG Air Quality Sensor</t>
+          <t>Smart Plug</t>
         </is>
       </c>
       <c r="D178" s="6" t="inlineStr">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="E178" s="6" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Smart plug</t>
         </is>
       </c>
       <c r="G178" s="7" t="inlineStr"/>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>LG Door and Window Sensor</t>
+          <t>LG Air Quality Sensor</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr"/>
@@ -6520,7 +6520,7 @@
       </c>
       <c r="C180" s="7" t="inlineStr">
         <is>
-          <t>LG Motion Sensor</t>
+          <t>LG Door and Window Sensor</t>
         </is>
       </c>
       <c r="D180" s="6" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>Presence</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="G180" s="7" t="inlineStr"/>
@@ -6551,22 +6551,22 @@
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>LG SIGNATURE Smart InstaView® Over-the-Range Microwave Oven</t>
+          <t>LG Motion Sensor</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Presence</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr"/>
@@ -6582,22 +6582,22 @@
       </c>
       <c r="C182" s="7" t="inlineStr">
         <is>
-          <t>LG Smart Button (1 Button)</t>
+          <t>LG SIGNATURE Smart InstaView® Over-the-Range Microwave Oven</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
         <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="F182" s="6" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="F182" s="6" t="inlineStr">
-        <is>
-          <t>Switch</t>
         </is>
       </c>
       <c r="G182" s="7" t="inlineStr"/>
@@ -6613,7 +6613,7 @@
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>LG Smart Button (2 Button)</t>
+          <t>LG Smart Button (1 Button)</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="C184" s="7" t="inlineStr">
         <is>
-          <t>LG Smart Plug</t>
+          <t>LG Smart Button (2 Button)</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>Smart plug</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G184" s="7" t="inlineStr"/>
@@ -6675,7 +6675,7 @@
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>LG Smart Wall Switch (1 Button)</t>
+          <t>LG Smart Plug</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Smart plug</t>
         </is>
       </c>
       <c r="G185" s="5" t="inlineStr"/>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="C186" s="7" t="inlineStr">
         <is>
-          <t>LG Smart Wall Switch (2 Button)</t>
+          <t>LG Smart Wall Switch (1 Button)</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>LG Smart Wall Switch (3 Button)</t>
+          <t>LG Smart Wall Switch (2 Button)</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="C188" s="7" t="inlineStr">
         <is>
-          <t>LG Temperature and Humidity Sensor</t>
+          <t>LG Smart Wall Switch (3 Button)</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="E188" s="6" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G188" s="7" t="inlineStr"/>
@@ -6799,22 +6799,22 @@
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>LG ThinQ ON</t>
+          <t>LG Temperature and Humidity Sensor</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>Smart speaker</t>
+          <t>Temperature</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr"/>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="C190" s="7" t="inlineStr">
         <is>
-          <t>LG webOS TV</t>
+          <t>LG ThinQ ON</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>Smart speaker</t>
         </is>
       </c>
       <c r="G190" s="7" t="inlineStr"/>
@@ -6856,27 +6856,27 @@
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>LOCKIN (U.S.) INC.</t>
+          <t>LG Electronics</t>
         </is>
       </c>
       <c r="C191" s="5" t="inlineStr">
         <is>
-          <t>Veno Pro</t>
+          <t>LG webOS TV</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G191" s="5" t="inlineStr"/>
@@ -6887,27 +6887,27 @@
       </c>
       <c r="B192" s="7" t="inlineStr">
         <is>
-          <t>Lab126</t>
+          <t>LOCKIN (U.S.) INC.</t>
         </is>
       </c>
       <c r="C192" s="7" t="inlineStr">
         <is>
-          <t>Echo (E78T24)</t>
+          <t>Veno Pro</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="G192" s="7" t="inlineStr"/>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="C193" s="5" t="inlineStr">
         <is>
-          <t>Echo (MA49CA)</t>
+          <t>Echo (E78T24)</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C194" s="7" t="inlineStr">
         <is>
-          <t>Echo (MD6NE4)</t>
+          <t>Echo (MA49CA)</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="C195" s="5" t="inlineStr">
         <is>
-          <t>Echo (P8Z7MN)</t>
+          <t>Echo (MD6NE4)</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="C196" s="7" t="inlineStr">
         <is>
-          <t>Echo (PE4Z26)</t>
+          <t>Echo (P8Z7MN)</t>
         </is>
       </c>
       <c r="D196" s="6" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="C197" s="5" t="inlineStr">
         <is>
-          <t>Echo gen 4</t>
+          <t>Echo (PE4Z26)</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>Smart speaker</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr"/>
@@ -7078,12 +7078,12 @@
       </c>
       <c r="C198" s="7" t="inlineStr">
         <is>
-          <t>eero 6</t>
+          <t>Echo gen 4</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>Wi-Fi Access Point</t>
+          <t>Smart speaker</t>
         </is>
       </c>
       <c r="G198" s="7" t="inlineStr"/>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>eero 6+</t>
+          <t>eero 6</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="C200" s="7" t="inlineStr">
         <is>
-          <t>eero Beacon</t>
+          <t>eero 6+</t>
         </is>
       </c>
       <c r="D200" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="C201" s="5" t="inlineStr">
         <is>
-          <t>eero Max 7</t>
+          <t>eero Beacon</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C202" s="7" t="inlineStr">
         <is>
-          <t>eero PoE 6</t>
+          <t>eero Max 7</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C203" s="5" t="inlineStr">
         <is>
-          <t>eero PoE Gateway</t>
+          <t>eero PoE 6</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Wi-Fi Access Point</t>
         </is>
       </c>
       <c r="G203" s="5" t="inlineStr"/>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="C204" s="7" t="inlineStr">
         <is>
-          <t>eero Pro (Wi-Fi 5)</t>
+          <t>eero PoE Gateway</t>
         </is>
       </c>
       <c r="D204" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E204" s="6" t="inlineStr">
@@ -7279,7 +7279,7 @@
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>Wi-Fi Access Point</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G204" s="7" t="inlineStr"/>
@@ -7295,12 +7295,12 @@
       </c>
       <c r="C205" s="5" t="inlineStr">
         <is>
-          <t>eero Pro (Wi-Fi 6)</t>
+          <t>eero Pro (Wi-Fi 5)</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E205" s="4" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="C206" s="7" t="inlineStr">
         <is>
-          <t>eero Pro 6E</t>
+          <t>eero Pro (Wi-Fi 6)</t>
         </is>
       </c>
       <c r="D206" s="6" t="inlineStr">
@@ -7352,27 +7352,27 @@
       </c>
       <c r="B207" s="5" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>Lab126</t>
         </is>
       </c>
       <c r="C207" s="5" t="inlineStr">
         <is>
-          <t>Netatmo Smart Security Sensor</t>
+          <t>eero Pro 6E</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Wi-Fi Access Point</t>
         </is>
       </c>
       <c r="G207" s="5" t="inlineStr"/>
@@ -7383,12 +7383,12 @@
       </c>
       <c r="B208" s="7" t="inlineStr">
         <is>
-          <t>Level Home Inc.</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="C208" s="7" t="inlineStr">
         <is>
-          <t>Level Lock+ (Matter)</t>
+          <t>Netatmo Smart Security Sensor</t>
         </is>
       </c>
       <c r="D208" s="6" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="E208" s="6" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="G208" s="7" t="inlineStr"/>
@@ -7414,12 +7414,12 @@
       </c>
       <c r="B209" s="5" t="inlineStr">
         <is>
-          <t>Lumi United Technology Co., Ltd</t>
+          <t>Level Home Inc.</t>
         </is>
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t>Aqara Door and Window Sensor P2</t>
+          <t>Level Lock+ (Matter)</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr"/>
@@ -7450,22 +7450,22 @@
       </c>
       <c r="C210" s="7" t="inlineStr">
         <is>
-          <t>Aqara Hub M3</t>
+          <t>Aqara Door and Window Sensor P2</t>
         </is>
       </c>
       <c r="D210" s="6" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="G210" s="7" t="inlineStr"/>
@@ -7481,22 +7481,22 @@
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
-          <t>Aqara Motion and Light Sensor P2</t>
+          <t>Aqara Hub M3</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>Presence</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G211" s="5" t="inlineStr"/>
@@ -7512,7 +7512,7 @@
       </c>
       <c r="C212" s="7" t="inlineStr">
         <is>
-          <t>Aqara Smart Lock J200 / J200 Set</t>
+          <t>Aqara Motion and Light Sensor P2</t>
         </is>
       </c>
       <c r="D212" s="6" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="E212" s="6" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Presence</t>
         </is>
       </c>
       <c r="G212" s="7" t="inlineStr"/>
@@ -7543,22 +7543,22 @@
       </c>
       <c r="C213" s="5" t="inlineStr">
         <is>
-          <t>Aqara Thread Module LM22-G24-HP</t>
+          <t>Aqara Smart Lock J200 / J200 Set</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E213" s="4" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr"/>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="C214" s="7" t="inlineStr">
         <is>
-          <t>Aqara Thread Module LM22-G24-LP</t>
+          <t>Aqara Thread Module LM22-G24-HP</t>
         </is>
       </c>
       <c r="D214" s="6" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>Camera Hub G350</t>
+          <t>Aqara Thread Module LM22-G24-LP</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="F215" s="4" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="F215" s="4" t="inlineStr">
-        <is>
-          <t>Hub</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr"/>
@@ -7636,7 +7636,7 @@
       </c>
       <c r="C216" s="7" t="inlineStr">
         <is>
-          <t>Camera Hub G5 Pro (PoE)</t>
+          <t>Camera Hub G350</t>
         </is>
       </c>
       <c r="D216" s="6" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="E216" s="6" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F216" s="6" t="inlineStr">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>Camera Hub G5 Pro (Wi-Fi)</t>
+          <t>Camera Hub G5 Pro (PoE)</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
@@ -7698,22 +7698,22 @@
       </c>
       <c r="C218" s="7" t="inlineStr">
         <is>
-          <t>Climate Sensor W100</t>
+          <t>Camera Hub G5 Pro (Wi-Fi)</t>
         </is>
       </c>
       <c r="D218" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G218" s="7" t="inlineStr"/>
@@ -7729,7 +7729,7 @@
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>Constant Current Driver T3 (40W)</t>
+          <t>Climate Sensor W100</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
@@ -7739,12 +7739,12 @@
       </c>
       <c r="E219" s="4" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Temperature</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr"/>
@@ -7760,7 +7760,7 @@
       </c>
       <c r="C220" s="7" t="inlineStr">
         <is>
-          <t>Constant Current Driver T3 (75W)</t>
+          <t>Constant Current Driver T3 (40W)</t>
         </is>
       </c>
       <c r="D220" s="6" t="inlineStr">
@@ -7791,22 +7791,22 @@
       </c>
       <c r="C221" s="5" t="inlineStr">
         <is>
-          <t>DIN Rail Hub AX100M</t>
+          <t>Constant Current Driver T3 (75W)</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E221" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="G221" s="5" t="inlineStr"/>
@@ -7822,22 +7822,22 @@
       </c>
       <c r="C222" s="7" t="inlineStr">
         <is>
-          <t>Dimmer Switch H2 EU</t>
+          <t>DIN Rail Hub AX100M</t>
         </is>
       </c>
       <c r="D222" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E222" s="6" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G222" s="7" t="inlineStr"/>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
-          <t>Dimmer Switch H2 US</t>
+          <t>Dimmer Switch H2 EU</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
@@ -7884,22 +7884,22 @@
       </c>
       <c r="C224" s="7" t="inlineStr">
         <is>
-          <t>Doorbell Camera Hub G410</t>
+          <t>Dimmer Switch H2 US</t>
         </is>
       </c>
       <c r="D224" s="6" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E224" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G224" s="7" t="inlineStr"/>
@@ -7915,7 +7915,7 @@
       </c>
       <c r="C225" s="5" t="inlineStr">
         <is>
-          <t>Edge Hub GX300M</t>
+          <t>Doorbell Camera Hub G410</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="C226" s="7" t="inlineStr">
         <is>
-          <t>Edge Hub M300</t>
+          <t>Edge Hub GX300M</t>
         </is>
       </c>
       <c r="D226" s="6" t="inlineStr">
@@ -7977,22 +7977,22 @@
       </c>
       <c r="C227" s="5" t="inlineStr">
         <is>
-          <t>Floor Heating Thermostat W500</t>
+          <t>Edge Hub M300</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>Heating</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G227" s="5" t="inlineStr"/>
@@ -8008,22 +8008,22 @@
       </c>
       <c r="C228" s="7" t="inlineStr">
         <is>
-          <t>Hub AX200M</t>
+          <t>Floor Heating Thermostat W500</t>
         </is>
       </c>
       <c r="D228" s="6" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E228" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="F228" s="6" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>Heating</t>
         </is>
       </c>
       <c r="G228" s="7" t="inlineStr"/>
@@ -8034,27 +8034,27 @@
       </c>
       <c r="B229" s="5" t="inlineStr">
         <is>
-          <t>MEAN WELL ENTERPRISES CO., LTD.</t>
+          <t>Lumi United Technology Co., Ltd</t>
         </is>
       </c>
       <c r="C229" s="5" t="inlineStr">
         <is>
-          <t>LED Driver</t>
+          <t>Hub AX200M</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E229" s="4" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G229" s="5" t="inlineStr"/>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="B230" s="7" t="inlineStr">
         <is>
-          <t>MIWA LOCK Co., LTD.</t>
+          <t>MEAN WELL ENTERPRISES CO., LTD.</t>
         </is>
       </c>
       <c r="C230" s="7" t="inlineStr">
         <is>
-          <t>DTPGM</t>
+          <t>LED Driver</t>
         </is>
       </c>
       <c r="D230" s="6" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="E230" s="6" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G230" s="7" t="inlineStr"/>
@@ -8096,12 +8096,12 @@
       </c>
       <c r="B231" s="5" t="inlineStr">
         <is>
-          <t>MMB Networks</t>
+          <t>MIWA LOCK Co., LTD.</t>
         </is>
       </c>
       <c r="C231" s="5" t="inlineStr">
         <is>
-          <t>Thread Mesh Extender</t>
+          <t>DTPGM</t>
         </is>
       </c>
       <c r="D231" s="4" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="E231" s="4" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="G231" s="5" t="inlineStr"/>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="B232" s="7" t="inlineStr">
         <is>
-          <t>Mayer &amp; Co Beschläge GmbH</t>
+          <t>MMB Networks</t>
         </is>
       </c>
       <c r="C232" s="7" t="inlineStr">
         <is>
-          <t>Sense by MACO | Casement</t>
+          <t>Thread Mesh Extender</t>
         </is>
       </c>
       <c r="D232" s="6" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="E232" s="6" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G232" s="7" t="inlineStr"/>
@@ -8163,7 +8163,7 @@
       </c>
       <c r="C233" s="5" t="inlineStr">
         <is>
-          <t>Sense by MACO | Door</t>
+          <t>Sense by MACO | Casement</t>
         </is>
       </c>
       <c r="D233" s="4" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="C234" s="7" t="inlineStr">
         <is>
-          <t>Sense by MACO | Universal</t>
+          <t>Sense by MACO | Door</t>
         </is>
       </c>
       <c r="D234" s="6" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="C235" s="5" t="inlineStr">
         <is>
-          <t>Sense by MACO | Window Pro T&amp;T</t>
+          <t>Sense by MACO | Universal</t>
         </is>
       </c>
       <c r="D235" s="4" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="C236" s="7" t="inlineStr">
         <is>
-          <t>Sense by MACO | Window T&amp;T</t>
+          <t>Sense by MACO | Window Pro T&amp;T</t>
         </is>
       </c>
       <c r="D236" s="6" t="inlineStr">
@@ -8282,27 +8282,27 @@
       </c>
       <c r="B237" s="5" t="inlineStr">
         <is>
-          <t>Mediatek Inc</t>
+          <t>Mayer &amp; Co Beschläge GmbH</t>
         </is>
       </c>
       <c r="C237" s="5" t="inlineStr">
         <is>
-          <t>Airoha AB16xx</t>
+          <t>Sense by MACO | Window T&amp;T</t>
         </is>
       </c>
       <c r="D237" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E237" s="4" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr"/>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="C238" s="7" t="inlineStr">
         <is>
-          <t>MT7902</t>
+          <t>Airoha AB16xx</t>
         </is>
       </c>
       <c r="D238" s="6" t="inlineStr">
@@ -8349,7 +8349,7 @@
       </c>
       <c r="C239" s="5" t="inlineStr">
         <is>
-          <t>MT7903 Border Router Assembly</t>
+          <t>MT7902</t>
         </is>
       </c>
       <c r="D239" s="4" t="inlineStr">
@@ -8375,12 +8375,12 @@
       </c>
       <c r="B240" s="7" t="inlineStr">
         <is>
-          <t>Mediola connected living AG</t>
+          <t>Mediatek Inc</t>
         </is>
       </c>
       <c r="C240" s="7" t="inlineStr">
         <is>
-          <t>SH 2.0 Matter over Thread Module</t>
+          <t>MT7903 Border Router Assembly</t>
         </is>
       </c>
       <c r="D240" s="6" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="E240" s="6" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="F240" s="6" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="B241" s="5" t="inlineStr">
         <is>
-          <t>Microchip Technology Inc</t>
+          <t>Mediola connected living AG</t>
         </is>
       </c>
       <c r="C241" s="5" t="inlineStr">
         <is>
-          <t>PIC32CX-BZ2 and WBZ451</t>
+          <t>SH 2.0 Matter over Thread Module</t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="C242" s="7" t="inlineStr">
         <is>
-          <t>WBZ451HPE</t>
+          <t>PIC32CX-BZ2 and WBZ451</t>
         </is>
       </c>
       <c r="D242" s="6" t="inlineStr">
@@ -8468,27 +8468,27 @@
       </c>
       <c r="B243" s="5" t="inlineStr">
         <is>
-          <t>Mighton Products Ltd</t>
+          <t>Microchip Technology Inc</t>
         </is>
       </c>
       <c r="C243" s="5" t="inlineStr">
         <is>
-          <t>Avia USA Deadbolt</t>
+          <t>WBZ451HPE</t>
         </is>
       </c>
       <c r="D243" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E243" s="4" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="F243" s="4" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr"/>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="B244" s="7" t="inlineStr">
         <is>
-          <t>Mikrotikls SIA</t>
+          <t>Mighton Products Ltd</t>
         </is>
       </c>
       <c r="C244" s="7" t="inlineStr">
         <is>
-          <t>Indoor Air Quality Monitor</t>
+          <t>Avia USA Deadbolt</t>
         </is>
       </c>
       <c r="D244" s="6" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="E244" s="6" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="G244" s="7" t="inlineStr"/>
@@ -8530,27 +8530,27 @@
       </c>
       <c r="B245" s="5" t="inlineStr">
         <is>
-          <t>NAMI AI</t>
+          <t>Mikrotikls SIA</t>
         </is>
       </c>
       <c r="C245" s="5" t="inlineStr">
         <is>
-          <t>Mesh Sensor</t>
+          <t>Indoor Air Quality Monitor</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E245" s="4" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F245" s="4" t="inlineStr">
         <is>
-          <t>Smart plug</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="G245" s="5" t="inlineStr"/>
@@ -8561,12 +8561,12 @@
       </c>
       <c r="B246" s="7" t="inlineStr">
         <is>
-          <t>NXP Semiconductors</t>
+          <t>NAMI AI</t>
         </is>
       </c>
       <c r="C246" s="7" t="inlineStr">
         <is>
-          <t>K32W061 / K32W041</t>
+          <t>Mesh Sensor</t>
         </is>
       </c>
       <c r="D246" s="6" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="E246" s="6" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Smart plug</t>
         </is>
       </c>
       <c r="G246" s="7" t="inlineStr"/>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="C247" s="5" t="inlineStr">
         <is>
-          <t>K32W148</t>
+          <t>K32W061 / K32W041</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="C248" s="7" t="inlineStr">
         <is>
-          <t>NXP MCX W71</t>
+          <t>K32W148</t>
         </is>
       </c>
       <c r="D248" s="6" t="inlineStr">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="C249" s="5" t="inlineStr">
         <is>
-          <t>NXP MCX W72</t>
+          <t>NXP MCX W71</t>
         </is>
       </c>
       <c r="D249" s="4" t="inlineStr">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C250" s="7" t="inlineStr">
         <is>
-          <t>NXP RW612 Wireless MCU with Integrated Tri-Radio</t>
+          <t>NXP MCX W72</t>
         </is>
       </c>
       <c r="D250" s="6" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="C251" s="5" t="inlineStr">
         <is>
-          <t>NXP RW612 Wireless MCU with Integrated Tri-Radio OTBR</t>
+          <t>NXP RW612 Wireless MCU with Integrated Tri-Radio</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="C253" s="5" t="inlineStr">
         <is>
-          <t>NXP i.MX MPU with IW610 Tri-Radio OTBR</t>
+          <t>NXP RW612 Wireless MCU with Integrated Tri-Radio OTBR</t>
         </is>
       </c>
       <c r="D253" s="4" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="C254" s="7" t="inlineStr">
         <is>
-          <t>NXP i.MX MPU with IW612 Tri-Radio OTBR</t>
+          <t>NXP i.MX MPU with IW610 Tri-Radio OTBR</t>
         </is>
       </c>
       <c r="D254" s="6" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="C255" s="5" t="inlineStr">
         <is>
-          <t>NXP i.MX RT Crossover MCU + K32W061/41</t>
+          <t>NXP i.MX MPU with IW612 Tri-Radio OTBR</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="C256" s="7" t="inlineStr">
         <is>
-          <t>NXP i.MX8M RT Crossover MCU + IW612 Tri-Radio</t>
+          <t>NXP i.MX RT Crossover MCU + K32W061/41</t>
         </is>
       </c>
       <c r="D256" s="6" t="inlineStr">
@@ -8907,7 +8907,7 @@
       </c>
       <c r="C257" s="5" t="inlineStr">
         <is>
-          <t>i.MX8M MPU + IW612 Tri-Radio</t>
+          <t>NXP i.MX8M RT Crossover MCU + IW612 Tri-Radio</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="C258" s="7" t="inlineStr">
         <is>
-          <t>i.MX8M MPU + IW612 Tri-Radio (BR)</t>
+          <t>i.MX8M MPU + IW612 Tri-Radio</t>
         </is>
       </c>
       <c r="D258" s="6" t="inlineStr">
@@ -8964,27 +8964,27 @@
       </c>
       <c r="B259" s="5" t="inlineStr">
         <is>
-          <t>Nanoleaf</t>
+          <t>NXP Semiconductors</t>
         </is>
       </c>
       <c r="C259" s="5" t="inlineStr">
         <is>
-          <t>Caveman A19/A60 Light Bulb</t>
+          <t>i.MX8M MPU + IW612 Tri-Radio (BR)</t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E259" s="4" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="F259" s="4" t="inlineStr">
         <is>
-          <t>Bulb</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr"/>
@@ -9000,7 +9000,7 @@
       </c>
       <c r="C260" s="7" t="inlineStr">
         <is>
-          <t>Caveman Smart 6" Downlight</t>
+          <t>Caveman A19/A60 Light Bulb</t>
         </is>
       </c>
       <c r="D260" s="6" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="C261" s="5" t="inlineStr">
         <is>
-          <t>Essentials A19 Bulb</t>
+          <t>Caveman Smart 6" Downlight</t>
         </is>
       </c>
       <c r="D261" s="4" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="C262" s="7" t="inlineStr">
         <is>
-          <t>Essentials Lightstrip</t>
+          <t>Essentials A19 Bulb</t>
         </is>
       </c>
       <c r="D262" s="6" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="F262" s="6" t="inlineStr">
         <is>
-          <t>Lightstrip</t>
+          <t>Bulb</t>
         </is>
       </c>
       <c r="G262" s="7" t="inlineStr"/>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="C263" s="5" t="inlineStr">
         <is>
-          <t>Nanoleaf Essentials A19/A60 Smart Bulb</t>
+          <t>Essentials Lightstrip</t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="F263" s="4" t="inlineStr">
         <is>
-          <t>Bulb</t>
+          <t>Lightstrip</t>
         </is>
       </c>
       <c r="G263" s="5" t="inlineStr"/>
@@ -9124,7 +9124,7 @@
       </c>
       <c r="C264" s="7" t="inlineStr">
         <is>
-          <t>Nanoleaf Essentials BR30 Smart Bulb</t>
+          <t>Nanoleaf Essentials A19/A60 Smart Bulb</t>
         </is>
       </c>
       <c r="D264" s="6" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="C265" s="5" t="inlineStr">
         <is>
-          <t>Nanoleaf Essentials GU10 Smart Bulb</t>
+          <t>Nanoleaf Essentials BR30 Smart Bulb</t>
         </is>
       </c>
       <c r="D265" s="4" t="inlineStr">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="C266" s="7" t="inlineStr">
         <is>
-          <t>Nanoleaf Essentials Lightstrip</t>
+          <t>Nanoleaf Essentials GU10 Smart Bulb</t>
         </is>
       </c>
       <c r="D266" s="6" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="F266" s="6" t="inlineStr">
         <is>
-          <t>Lightstrip</t>
+          <t>Bulb</t>
         </is>
       </c>
       <c r="G266" s="7" t="inlineStr"/>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="C267" s="5" t="inlineStr">
         <is>
-          <t>Nanoleaf Essentials Smart Ceiling Light</t>
+          <t>Nanoleaf Essentials Lightstrip</t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="F267" s="4" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Lightstrip</t>
         </is>
       </c>
       <c r="G267" s="5" t="inlineStr"/>
@@ -9248,7 +9248,7 @@
       </c>
       <c r="C268" s="7" t="inlineStr">
         <is>
-          <t>Nanoleaf Essentials Smart Recessed Downlight</t>
+          <t>Nanoleaf Essentials Smart Ceiling Light</t>
         </is>
       </c>
       <c r="D268" s="6" t="inlineStr">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="F268" s="6" t="inlineStr">
         <is>
-          <t>Bulb</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="G268" s="7" t="inlineStr"/>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="C269" s="5" t="inlineStr">
         <is>
-          <t>Umbra Cono Lamp</t>
+          <t>Nanoleaf Essentials Smart Recessed Downlight</t>
         </is>
       </c>
       <c r="D269" s="4" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="F269" s="4" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Bulb</t>
         </is>
       </c>
       <c r="G269" s="5" t="inlineStr"/>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C270" s="7" t="inlineStr">
         <is>
-          <t>Umbra Cup Lamp</t>
+          <t>Umbra Cono Lamp</t>
         </is>
       </c>
       <c r="D270" s="6" t="inlineStr">
@@ -9336,12 +9336,12 @@
       </c>
       <c r="B271" s="5" t="inlineStr">
         <is>
-          <t>Ningbo Dooya Mechanic &amp; Electronic Technology Co., Ltd</t>
+          <t>Nanoleaf</t>
         </is>
       </c>
       <c r="C271" s="5" t="inlineStr">
         <is>
-          <t>Thread Window Covering Motor</t>
+          <t>Umbra Cup Lamp</t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr">
@@ -9351,12 +9351,12 @@
       </c>
       <c r="E271" s="4" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F271" s="4" t="inlineStr">
         <is>
-          <t>Blind</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr"/>
@@ -9367,27 +9367,27 @@
       </c>
       <c r="B272" s="7" t="inlineStr">
         <is>
-          <t>Nordic Semiconductor ASA</t>
+          <t>Ningbo Dooya Mechanic &amp; Electronic Technology Co., Ltd</t>
         </is>
       </c>
       <c r="C272" s="7" t="inlineStr">
         <is>
-          <t>Nordic Semiconductor nRF54Lxx – nRF Connect SDK</t>
+          <t>Thread Window Covering Motor</t>
         </is>
       </c>
       <c r="D272" s="6" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E272" s="6" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="F272" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Blind</t>
         </is>
       </c>
       <c r="G272" s="7" t="inlineStr"/>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="C273" s="5" t="inlineStr">
         <is>
-          <t>nRF52833 nRF Connect SDK</t>
+          <t>Nordic Semiconductor nRF54Lxx – nRF Connect SDK</t>
         </is>
       </c>
       <c r="D273" s="4" t="inlineStr">
@@ -9434,7 +9434,7 @@
       </c>
       <c r="C274" s="7" t="inlineStr">
         <is>
-          <t>nRF52840 nRF Connect SDK</t>
+          <t>nRF52833 nRF Connect SDK</t>
         </is>
       </c>
       <c r="D274" s="6" t="inlineStr">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="C275" s="5" t="inlineStr">
         <is>
-          <t>nRF5340 nRF Connect SDK</t>
+          <t>nRF52840 nRF Connect SDK</t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr">
@@ -9491,27 +9491,27 @@
       </c>
       <c r="B276" s="7" t="inlineStr">
         <is>
-          <t>Nuki Home Solutions GmbH</t>
+          <t>Nordic Semiconductor ASA</t>
         </is>
       </c>
       <c r="C276" s="7" t="inlineStr">
         <is>
-          <t>Nuki Smart Lock (4th Generation)</t>
+          <t>nRF5340 nRF Connect SDK</t>
         </is>
       </c>
       <c r="D276" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E276" s="6" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="F276" s="6" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G276" s="7" t="inlineStr"/>
@@ -9527,7 +9527,7 @@
       </c>
       <c r="C277" s="5" t="inlineStr">
         <is>
-          <t>Nuki Smart Lock Go</t>
+          <t>Nuki Smart Lock (4th Generation)</t>
         </is>
       </c>
       <c r="D277" s="4" t="inlineStr">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C278" s="7" t="inlineStr">
         <is>
-          <t>Nuki Smart Lock Pro</t>
+          <t>Nuki Smart Lock Go</t>
         </is>
       </c>
       <c r="D278" s="6" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="C279" s="5" t="inlineStr">
         <is>
-          <t>Nuki Smart Lock Pro (4th Generation)</t>
+          <t>Nuki Smart Lock Pro</t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="C280" s="7" t="inlineStr">
         <is>
-          <t>Nuki Smart Lock Ultra</t>
+          <t>Nuki Smart Lock Pro (4th Generation)</t>
         </is>
       </c>
       <c r="D280" s="6" t="inlineStr">
@@ -9646,27 +9646,27 @@
       </c>
       <c r="B281" s="5" t="inlineStr">
         <is>
-          <t>ORANGE</t>
+          <t>Nuki Home Solutions GmbH</t>
         </is>
       </c>
       <c r="C281" s="5" t="inlineStr">
         <is>
-          <t>Livebox S</t>
+          <t>Nuki Smart Lock Ultra</t>
         </is>
       </c>
       <c r="D281" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E281" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F281" s="4" t="inlineStr">
         <is>
-          <t>Wi-Fi Access Point</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="G281" s="5" t="inlineStr"/>
@@ -9677,27 +9677,27 @@
       </c>
       <c r="B282" s="7" t="inlineStr">
         <is>
-          <t>PIN Genie Inc, DBA Lockly</t>
+          <t>ORANGE</t>
         </is>
       </c>
       <c r="C282" s="7" t="inlineStr">
         <is>
-          <t>Lockly Smart Lock (PGD638)</t>
+          <t>Livebox S</t>
         </is>
       </c>
       <c r="D282" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E282" s="6" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F282" s="6" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Wi-Fi Access Point</t>
         </is>
       </c>
       <c r="G282" s="7" t="inlineStr"/>
@@ -9713,7 +9713,7 @@
       </c>
       <c r="C283" s="5" t="inlineStr">
         <is>
-          <t>Lockly Smart Lock (PGD738)</t>
+          <t>Lockly Smart Lock (PGD638)</t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr">
@@ -9739,12 +9739,12 @@
       </c>
       <c r="B284" s="7" t="inlineStr">
         <is>
-          <t>Qingdao Yeelink Information Technology Co., Ltd</t>
+          <t>PIN Genie Inc, DBA Lockly</t>
         </is>
       </c>
       <c r="C284" s="7" t="inlineStr">
         <is>
-          <t>Smart Switch</t>
+          <t>Lockly Smart Lock (PGD738)</t>
         </is>
       </c>
       <c r="D284" s="6" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="E284" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F284" s="6" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="G284" s="7" t="inlineStr"/>
@@ -9775,12 +9775,12 @@
       </c>
       <c r="C285" s="5" t="inlineStr">
         <is>
-          <t>Yeelight Pro Smart Home Hub</t>
+          <t>Smart Switch</t>
         </is>
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E285" s="4" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="F285" s="4" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G285" s="5" t="inlineStr"/>
@@ -9806,22 +9806,22 @@
       </c>
       <c r="C286" s="7" t="inlineStr">
         <is>
-          <t>Yeelight Pro Torkey Smart RGBCW LED bulb</t>
+          <t>Yeelight Pro Smart Home Hub</t>
         </is>
       </c>
       <c r="D286" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E286" s="6" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>Bulb</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G286" s="7" t="inlineStr"/>
@@ -9837,7 +9837,7 @@
       </c>
       <c r="C287" s="5" t="inlineStr">
         <is>
-          <t>Yeelight RGBlC Smart LED Neon Rope Light</t>
+          <t>Yeelight Pro Torkey Smart RGBCW LED bulb</t>
         </is>
       </c>
       <c r="D287" s="4" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="F287" s="4" t="inlineStr">
         <is>
-          <t>Lightstrip</t>
+          <t>Bulb</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr"/>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="C288" s="7" t="inlineStr">
         <is>
-          <t>Yeelight Smart Ceiling Fan-Light S1</t>
+          <t>Yeelight RGBlC Smart LED Neon Rope Light</t>
         </is>
       </c>
       <c r="D288" s="6" t="inlineStr">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="F288" s="6" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Lightstrip</t>
         </is>
       </c>
       <c r="G288" s="7" t="inlineStr"/>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="C289" s="5" t="inlineStr">
         <is>
-          <t>Yeelight Smart LED Bedside Lamp D1</t>
+          <t>Yeelight Smart Ceiling Fan-Light S1</t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="C290" s="7" t="inlineStr">
         <is>
-          <t>Yeelight Smart LED Desk Lamp D1</t>
+          <t>Yeelight Smart LED Bedside Lamp D1</t>
         </is>
       </c>
       <c r="D290" s="6" t="inlineStr">
@@ -9956,27 +9956,27 @@
       </c>
       <c r="B291" s="5" t="inlineStr">
         <is>
-          <t>Qorvo Utrecht B.V.</t>
+          <t>Qingdao Yeelink Information Technology Co., Ltd</t>
         </is>
       </c>
       <c r="C291" s="5" t="inlineStr">
         <is>
-          <t>GP712</t>
+          <t>Yeelight Smart LED Desk Lamp D1</t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E291" s="4" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F291" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="G291" s="5" t="inlineStr"/>
@@ -9992,7 +9992,7 @@
       </c>
       <c r="C292" s="7" t="inlineStr">
         <is>
-          <t>QPG6105</t>
+          <t>GP712</t>
         </is>
       </c>
       <c r="D292" s="6" t="inlineStr">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="C293" s="5" t="inlineStr">
         <is>
-          <t>QPG6200</t>
+          <t>QPG6105</t>
         </is>
       </c>
       <c r="D293" s="4" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="C294" s="7" t="inlineStr">
         <is>
-          <t>QPG7015M</t>
+          <t>QPG6200</t>
         </is>
       </c>
       <c r="D294" s="6" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="B295" s="5" t="inlineStr">
         <is>
-          <t>Qualcomm Inc.</t>
+          <t>Qorvo Utrecht B.V.</t>
         </is>
       </c>
       <c r="C295" s="5" t="inlineStr">
         <is>
-          <t>QCA 4020</t>
+          <t>QPG7015M</t>
         </is>
       </c>
       <c r="D295" s="4" t="inlineStr">
@@ -10111,12 +10111,12 @@
       </c>
       <c r="B296" s="7" t="inlineStr">
         <is>
-          <t>Quectel Wireless Solutions Co., Ltd.</t>
+          <t>Qualcomm Inc.</t>
         </is>
       </c>
       <c r="C296" s="7" t="inlineStr">
         <is>
-          <t>KGM133S</t>
+          <t>QCA 4020</t>
         </is>
       </c>
       <c r="D296" s="6" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="E296" s="6" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="F296" s="6" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="B297" s="5" t="inlineStr">
         <is>
-          <t>Rafael Microelectronics, Inc.</t>
+          <t>Quectel Wireless Solutions Co., Ltd.</t>
         </is>
       </c>
       <c r="C297" s="5" t="inlineStr">
         <is>
-          <t>2.4G Wireless SOC E2</t>
+          <t>KGM133S</t>
         </is>
       </c>
       <c r="D297" s="4" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="E297" s="4" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="F297" s="4" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="C298" s="7" t="inlineStr">
         <is>
-          <t>RT582 + OpenThread SDK (V1.3.0)</t>
+          <t>2.4G Wireless SOC E2</t>
         </is>
       </c>
       <c r="D298" s="6" t="inlineStr">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C299" s="5" t="inlineStr">
         <is>
-          <t>RT583</t>
+          <t>RT582 + OpenThread SDK (V1.3.0)</t>
         </is>
       </c>
       <c r="D299" s="4" t="inlineStr">
@@ -10240,7 +10240,7 @@
       </c>
       <c r="C300" s="7" t="inlineStr">
         <is>
-          <t>Rafael RT584x</t>
+          <t>RT583</t>
         </is>
       </c>
       <c r="D300" s="6" t="inlineStr">
@@ -10271,22 +10271,22 @@
       </c>
       <c r="C301" s="5" t="inlineStr">
         <is>
-          <t>Smart Wall Switch</t>
+          <t>Rafael RT584x</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E301" s="4" t="inlineStr">
         <is>
+          <t>Chipset</t>
+        </is>
+      </c>
+      <c r="F301" s="4" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="F301" s="4" t="inlineStr">
-        <is>
-          <t>Switch</t>
         </is>
       </c>
       <c r="G301" s="5" t="inlineStr"/>
@@ -10297,27 +10297,27 @@
       </c>
       <c r="B302" s="7" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Rafael Microelectronics, Inc.</t>
         </is>
       </c>
       <c r="C302" s="7" t="inlineStr">
         <is>
-          <t>OT Border Router with Realtek AmebaSmart and RTL877x RCP</t>
+          <t>Smart Wall Switch</t>
         </is>
       </c>
       <c r="D302" s="6" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E302" s="6" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F302" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G302" s="7" t="inlineStr"/>
@@ -10333,7 +10333,7 @@
       </c>
       <c r="C303" s="5" t="inlineStr">
         <is>
-          <t>RTL877x series SoC</t>
+          <t>OT Border Router with Realtek AmebaSmart and RTL877x RCP</t>
         </is>
       </c>
       <c r="D303" s="4" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="E303" s="4" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="F303" s="4" t="inlineStr">
@@ -10364,7 +10364,7 @@
       </c>
       <c r="C304" s="7" t="inlineStr">
         <is>
-          <t>Realtek Wi-Fi+BT+802.15.4 3-in-1 NIC Combo SoC</t>
+          <t>RTL877x series SoC</t>
         </is>
       </c>
       <c r="D304" s="6" t="inlineStr">
@@ -10390,27 +10390,27 @@
       </c>
       <c r="B305" s="5" t="inlineStr">
         <is>
-          <t>Robert Bosch GmbH</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="C305" s="5" t="inlineStr">
         <is>
-          <t>Door-/Window Contact II [+M]</t>
+          <t>Realtek Wi-Fi+BT+802.15.4 3-in-1 NIC Combo SoC</t>
         </is>
       </c>
       <c r="D305" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E305" s="4" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="F305" s="4" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G305" s="5" t="inlineStr"/>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="C306" s="7" t="inlineStr">
         <is>
-          <t>Motion Detector II [+M]</t>
+          <t>Door-/Window Contact II [+M]</t>
         </is>
       </c>
       <c r="D306" s="6" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="F306" s="6" t="inlineStr">
         <is>
-          <t>Presence</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="G306" s="7" t="inlineStr"/>
@@ -10457,7 +10457,7 @@
       </c>
       <c r="C307" s="5" t="inlineStr">
         <is>
-          <t>Plug Compact [+M]</t>
+          <t>Motion Detector II [+M]</t>
         </is>
       </c>
       <c r="D307" s="4" t="inlineStr">
@@ -10467,12 +10467,12 @@
       </c>
       <c r="E307" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F307" s="4" t="inlineStr">
         <is>
-          <t>Smart plug</t>
+          <t>Presence</t>
         </is>
       </c>
       <c r="G307" s="5" t="inlineStr"/>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="C308" s="7" t="inlineStr">
         <is>
-          <t>Radiator Thermostat II [+M]</t>
+          <t>Plug Compact [+M]</t>
         </is>
       </c>
       <c r="D308" s="6" t="inlineStr">
@@ -10498,12 +10498,12 @@
       </c>
       <c r="E308" s="6" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F308" s="6" t="inlineStr">
         <is>
-          <t>Heating</t>
+          <t>Smart plug</t>
         </is>
       </c>
       <c r="G308" s="7" t="inlineStr"/>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="B309" s="5" t="inlineStr">
         <is>
-          <t>SENSEREO LIMITED</t>
+          <t>Robert Bosch GmbH</t>
         </is>
       </c>
       <c r="C309" s="5" t="inlineStr">
         <is>
-          <t>Sensereo Matter Smoke Alarm</t>
+          <t>Radiator Thermostat II [+M]</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="E309" s="4" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="F309" s="4" t="inlineStr">
         <is>
-          <t>Smoke alarm</t>
+          <t>Heating</t>
         </is>
       </c>
       <c r="G309" s="5" t="inlineStr"/>
@@ -10545,12 +10545,12 @@
       </c>
       <c r="B310" s="7" t="inlineStr">
         <is>
-          <t>SHENZHEN DEASINO TECHNOLOGY CO.,LTD</t>
+          <t>SENSEREO LIMITED</t>
         </is>
       </c>
       <c r="C310" s="7" t="inlineStr">
         <is>
-          <t>Matter LOCK</t>
+          <t>Sensereo Matter Smoke Alarm</t>
         </is>
       </c>
       <c r="D310" s="6" t="inlineStr">
@@ -10565,7 +10565,7 @@
       </c>
       <c r="F310" s="6" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Smoke alarm</t>
         </is>
       </c>
       <c r="G310" s="7" t="inlineStr"/>
@@ -10581,22 +10581,22 @@
       </c>
       <c r="C311" s="5" t="inlineStr">
         <is>
-          <t>Matter module</t>
+          <t>Matter LOCK</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E311" s="4" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F311" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="G311" s="5" t="inlineStr"/>
@@ -10607,27 +10607,27 @@
       </c>
       <c r="B312" s="7" t="inlineStr">
         <is>
-          <t>SIEGENIA-AUBI KG</t>
+          <t>SHENZHEN DEASINO TECHNOLOGY CO.,LTD</t>
         </is>
       </c>
       <c r="C312" s="7" t="inlineStr">
         <is>
-          <t>Smart Sensor</t>
+          <t>Matter module</t>
         </is>
       </c>
       <c r="D312" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E312" s="6" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="F312" s="6" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G312" s="7" t="inlineStr"/>
@@ -10643,7 +10643,7 @@
       </c>
       <c r="C313" s="5" t="inlineStr">
         <is>
-          <t>Smart Window Handle</t>
+          <t>Smart Sensor</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr">
@@ -10653,12 +10653,12 @@
       </c>
       <c r="E313" s="4" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F313" s="4" t="inlineStr">
         <is>
-          <t>Window lock</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="G313" s="5" t="inlineStr"/>
@@ -10669,27 +10669,27 @@
       </c>
       <c r="B314" s="7" t="inlineStr">
         <is>
-          <t>STMicroelectronics International N.V.</t>
+          <t>SIEGENIA-AUBI KG</t>
         </is>
       </c>
       <c r="C314" s="7" t="inlineStr">
         <is>
-          <t>STM32WB</t>
+          <t>Smart Window Handle</t>
         </is>
       </c>
       <c r="D314" s="6" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E314" s="6" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F314" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Window lock</t>
         </is>
       </c>
       <c r="G314" s="7" t="inlineStr"/>
@@ -10705,7 +10705,7 @@
       </c>
       <c r="C315" s="5" t="inlineStr">
         <is>
-          <t>STM32WB (Nucleo)</t>
+          <t>STM32WB</t>
         </is>
       </c>
       <c r="D315" s="4" t="inlineStr">
@@ -10715,7 +10715,7 @@
       </c>
       <c r="E315" s="4" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="F315" s="4" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="C316" s="7" t="inlineStr">
         <is>
-          <t>STM32WBA</t>
+          <t>STM32WB (Nucleo)</t>
         </is>
       </c>
       <c r="D316" s="6" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="C317" s="5" t="inlineStr">
         <is>
-          <t>STM32WBA65I-DK1 Discovery kit</t>
+          <t>STM32WBA</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="E317" s="4" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="F317" s="4" t="inlineStr">
@@ -10793,12 +10793,12 @@
       </c>
       <c r="B318" s="7" t="inlineStr">
         <is>
-          <t>Samsung SmartThings</t>
+          <t>STMicroelectronics International N.V.</t>
         </is>
       </c>
       <c r="C318" s="7" t="inlineStr">
         <is>
-          <t>Harman Kardon Virtuo</t>
+          <t>STM32WBA65I-DK1 Discovery kit</t>
         </is>
       </c>
       <c r="D318" s="6" t="inlineStr">
@@ -10808,12 +10808,12 @@
       </c>
       <c r="E318" s="6" t="inlineStr">
         <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="F318" s="6" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="F318" s="6" t="inlineStr">
-        <is>
-          <t>Smart speaker</t>
         </is>
       </c>
       <c r="G318" s="7" t="inlineStr"/>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="C319" s="5" t="inlineStr">
         <is>
-          <t>R95H</t>
+          <t>Harman Kardon Virtuo</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
@@ -10839,12 +10839,12 @@
       </c>
       <c r="E319" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F319" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Smart speaker</t>
         </is>
       </c>
       <c r="G319" s="5" t="inlineStr"/>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="C320" s="7" t="inlineStr">
         <is>
-          <t>S95H</t>
+          <t>R95H</t>
         </is>
       </c>
       <c r="D320" s="6" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="C321" s="5" t="inlineStr">
         <is>
-          <t>Samsung Monitor</t>
+          <t>S95H</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
@@ -10906,7 +10906,7 @@
       </c>
       <c r="F321" s="4" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G321" s="5" t="inlineStr"/>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="C322" s="7" t="inlineStr">
         <is>
-          <t>Samsung Signage</t>
+          <t>Samsung Monitor</t>
         </is>
       </c>
       <c r="D322" s="6" t="inlineStr">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="E322" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F322" s="6" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C323" s="5" t="inlineStr">
         <is>
-          <t>Samsung Smart TV</t>
+          <t>Samsung Signage</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
@@ -10963,7 +10963,7 @@
       </c>
       <c r="E323" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F323" s="4" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="C324" s="7" t="inlineStr">
         <is>
-          <t>Samsung SmartThings Hub V3</t>
+          <t>Samsung Smart TV</t>
         </is>
       </c>
       <c r="D324" s="6" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="E324" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F324" s="6" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="C325" s="5" t="inlineStr">
         <is>
-          <t>Samsung SmartThings Station</t>
+          <t>Samsung SmartThings Hub V3</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="C326" s="7" t="inlineStr">
         <is>
-          <t>Samsung Soundbar</t>
+          <t>Samsung SmartThings Station</t>
         </is>
       </c>
       <c r="D326" s="6" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="E326" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F326" s="6" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="C327" s="5" t="inlineStr">
         <is>
-          <t>SmartThings Hub V3</t>
+          <t>Samsung Soundbar</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="E327" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F327" s="4" t="inlineStr">
@@ -11103,27 +11103,27 @@
       </c>
       <c r="B328" s="7" t="inlineStr">
         <is>
-          <t>Savant</t>
+          <t>Samsung SmartThings</t>
         </is>
       </c>
       <c r="C328" s="7" t="inlineStr">
         <is>
-          <t>Smart window covering</t>
+          <t>SmartThings Hub V3</t>
         </is>
       </c>
       <c r="D328" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E328" s="6" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F328" s="6" t="inlineStr">
         <is>
-          <t>Curtain</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G328" s="7" t="inlineStr"/>
@@ -11134,12 +11134,12 @@
       </c>
       <c r="B329" s="5" t="inlineStr">
         <is>
-          <t>Schüco Polymer Technologies KG</t>
+          <t>Savant</t>
         </is>
       </c>
       <c r="C329" s="5" t="inlineStr">
         <is>
-          <t>Schüco Funksensor</t>
+          <t>Smart window covering</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
@@ -11149,12 +11149,12 @@
       </c>
       <c r="E329" s="4" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="F329" s="4" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Curtain</t>
         </is>
       </c>
       <c r="G329" s="5" t="inlineStr"/>
@@ -11165,12 +11165,12 @@
       </c>
       <c r="B330" s="7" t="inlineStr">
         <is>
-          <t>Secuyou</t>
+          <t>Schüco Polymer Technologies KG</t>
         </is>
       </c>
       <c r="C330" s="7" t="inlineStr">
         <is>
-          <t>Secuyou Smart Lock</t>
+          <t>Schüco Funksensor</t>
         </is>
       </c>
       <c r="D330" s="6" t="inlineStr">
@@ -11180,12 +11180,12 @@
       </c>
       <c r="E330" s="6" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F330" s="6" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="G330" s="7" t="inlineStr"/>
@@ -11196,27 +11196,27 @@
       </c>
       <c r="B331" s="5" t="inlineStr">
         <is>
-          <t>Sercomm Corporation</t>
+          <t>Secuyou</t>
         </is>
       </c>
       <c r="C331" s="5" t="inlineStr">
         <is>
-          <t>SAX2V1R</t>
+          <t>Secuyou Smart Lock</t>
         </is>
       </c>
       <c r="D331" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E331" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F331" s="4" t="inlineStr">
         <is>
-          <t>Wi-Fi Access Point</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="G331" s="5" t="inlineStr"/>
@@ -11232,7 +11232,7 @@
       </c>
       <c r="C332" s="7" t="inlineStr">
         <is>
-          <t>SBE1V1R</t>
+          <t>SAX2V1R</t>
         </is>
       </c>
       <c r="D332" s="6" t="inlineStr">
@@ -11242,7 +11242,7 @@
       </c>
       <c r="E332" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F332" s="6" t="inlineStr">
@@ -11258,27 +11258,27 @@
       </c>
       <c r="B333" s="5" t="inlineStr">
         <is>
-          <t>Shenzhen BOFU smart.co.,ltd</t>
+          <t>Sercomm Corporation</t>
         </is>
       </c>
       <c r="C333" s="5" t="inlineStr">
         <is>
-          <t>Blinds motor</t>
+          <t>SBE1V1R</t>
         </is>
       </c>
       <c r="D333" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E333" s="4" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F333" s="4" t="inlineStr">
         <is>
-          <t>Blind</t>
+          <t>Wi-Fi Access Point</t>
         </is>
       </c>
       <c r="G333" s="5" t="inlineStr"/>
@@ -11289,12 +11289,12 @@
       </c>
       <c r="B334" s="7" t="inlineStr">
         <is>
-          <t>Shenzhen Conex Intelligent Technology Co.,Ltd</t>
+          <t>Shenzhen BOFU smart.co.,ltd</t>
         </is>
       </c>
       <c r="C334" s="7" t="inlineStr">
         <is>
-          <t>Philips Smart Lock</t>
+          <t>Blinds motor</t>
         </is>
       </c>
       <c r="D334" s="6" t="inlineStr">
@@ -11304,12 +11304,12 @@
       </c>
       <c r="E334" s="6" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="F334" s="6" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Blind</t>
         </is>
       </c>
       <c r="G334" s="7" t="inlineStr"/>
@@ -11320,12 +11320,12 @@
       </c>
       <c r="B335" s="5" t="inlineStr">
         <is>
-          <t>Shenzhen Haojai Lianchuang Technology Co.,Ltd</t>
+          <t>Shenzhen Conex Intelligent Technology Co.,Ltd</t>
         </is>
       </c>
       <c r="C335" s="5" t="inlineStr">
         <is>
-          <t>HAOJAI Smart Switch</t>
+          <t>Philips Smart Lock</t>
         </is>
       </c>
       <c r="D335" s="4" t="inlineStr">
@@ -11335,12 +11335,12 @@
       </c>
       <c r="E335" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F335" s="4" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="G335" s="5" t="inlineStr"/>
@@ -11356,7 +11356,7 @@
       </c>
       <c r="C336" s="7" t="inlineStr">
         <is>
-          <t>Smart Curtain</t>
+          <t>HAOJAI Smart Switch</t>
         </is>
       </c>
       <c r="D336" s="6" t="inlineStr">
@@ -11366,12 +11366,12 @@
       </c>
       <c r="E336" s="6" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F336" s="6" t="inlineStr">
         <is>
-          <t>Blind</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G336" s="7" t="inlineStr"/>
@@ -11382,12 +11382,12 @@
       </c>
       <c r="B337" s="5" t="inlineStr">
         <is>
-          <t>Shenzhen Heiman Technology Co., Ltd.</t>
+          <t>Shenzhen Haojai Lianchuang Technology Co.,Ltd</t>
         </is>
       </c>
       <c r="C337" s="5" t="inlineStr">
         <is>
-          <t>Smart Carbon Monoxide Alarm</t>
+          <t>Smart Curtain</t>
         </is>
       </c>
       <c r="D337" s="4" t="inlineStr">
@@ -11397,12 +11397,12 @@
       </c>
       <c r="E337" s="4" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="F337" s="4" t="inlineStr">
         <is>
-          <t>Gas alarm</t>
+          <t>Blind</t>
         </is>
       </c>
       <c r="G337" s="5" t="inlineStr"/>
@@ -11418,7 +11418,7 @@
       </c>
       <c r="C338" s="7" t="inlineStr">
         <is>
-          <t>Smart Humidity &amp; Temperature Sensor</t>
+          <t>Smart Carbon Monoxide Alarm</t>
         </is>
       </c>
       <c r="D338" s="6" t="inlineStr">
@@ -11428,12 +11428,12 @@
       </c>
       <c r="E338" s="6" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F338" s="6" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>Gas alarm</t>
         </is>
       </c>
       <c r="G338" s="7" t="inlineStr"/>
@@ -11449,7 +11449,7 @@
       </c>
       <c r="C339" s="5" t="inlineStr">
         <is>
-          <t>Smart Plug (HS2SK series)</t>
+          <t>Smart Humidity &amp; Temperature Sensor</t>
         </is>
       </c>
       <c r="D339" s="4" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="E339" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F339" s="4" t="inlineStr">
         <is>
-          <t>Smart plug</t>
+          <t>Temperature</t>
         </is>
       </c>
       <c r="G339" s="5" t="inlineStr"/>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="C340" s="7" t="inlineStr">
         <is>
-          <t>Smart Smoke Alarm</t>
+          <t>Smart Plug (HS2SK series)</t>
         </is>
       </c>
       <c r="D340" s="6" t="inlineStr">
@@ -11490,12 +11490,12 @@
       </c>
       <c r="E340" s="6" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F340" s="6" t="inlineStr">
         <is>
-          <t>Smoke alarm</t>
+          <t>Smart plug</t>
         </is>
       </c>
       <c r="G340" s="7" t="inlineStr"/>
@@ -11511,7 +11511,7 @@
       </c>
       <c r="C341" s="5" t="inlineStr">
         <is>
-          <t>Smart Water Leakage Sensor</t>
+          <t>Smart Smoke Alarm</t>
         </is>
       </c>
       <c r="D341" s="4" t="inlineStr">
@@ -11521,12 +11521,12 @@
       </c>
       <c r="E341" s="4" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F341" s="4" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Smoke alarm</t>
         </is>
       </c>
       <c r="G341" s="5" t="inlineStr"/>
@@ -11537,12 +11537,12 @@
       </c>
       <c r="B342" s="7" t="inlineStr">
         <is>
-          <t>Shenzhen Sunricher Technology Co.,Ltd.</t>
+          <t>Shenzhen Heiman Technology Co., Ltd.</t>
         </is>
       </c>
       <c r="C342" s="7" t="inlineStr">
         <is>
-          <t>Sensor &amp; Switch</t>
+          <t>Smart Water Leakage Sensor</t>
         </is>
       </c>
       <c r="D342" s="6" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="F342" s="6" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="G342" s="7" t="inlineStr"/>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="C343" s="5" t="inlineStr">
         <is>
-          <t>Smart LED Dimmer Controller</t>
+          <t>Sensor &amp; Switch</t>
         </is>
       </c>
       <c r="D343" s="4" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="E343" s="4" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F343" s="4" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="G343" s="5" t="inlineStr"/>
@@ -11599,12 +11599,12 @@
       </c>
       <c r="B344" s="7" t="inlineStr">
         <is>
-          <t>Sichuan Changhong Neonet Technologies Co.,Ltd.</t>
+          <t>Shenzhen Sunricher Technology Co.,Ltd.</t>
         </is>
       </c>
       <c r="C344" s="7" t="inlineStr">
         <is>
-          <t>Door Sensor</t>
+          <t>Smart LED Dimmer Controller</t>
         </is>
       </c>
       <c r="D344" s="6" t="inlineStr">
@@ -11614,12 +11614,12 @@
       </c>
       <c r="E344" s="6" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F344" s="6" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G344" s="7" t="inlineStr"/>
@@ -11635,7 +11635,7 @@
       </c>
       <c r="C345" s="5" t="inlineStr">
         <is>
-          <t>Water Leak Detector</t>
+          <t>Door Sensor</t>
         </is>
       </c>
       <c r="D345" s="4" t="inlineStr">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="F345" s="4" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="G345" s="5" t="inlineStr"/>
@@ -11661,27 +11661,27 @@
       </c>
       <c r="B346" s="7" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Sichuan Changhong Neonet Technologies Co.,Ltd.</t>
         </is>
       </c>
       <c r="C346" s="7" t="inlineStr">
         <is>
-          <t>Thread Border Router</t>
+          <t>Water Leak Detector</t>
         </is>
       </c>
       <c r="D346" s="6" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E346" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F346" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="G346" s="7" t="inlineStr"/>
@@ -11697,22 +11697,22 @@
       </c>
       <c r="C347" s="5" t="inlineStr">
         <is>
-          <t>Wireless Room Sensor QAA2150KT</t>
+          <t>Thread Border Router</t>
         </is>
       </c>
       <c r="D347" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E347" s="4" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F347" s="4" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G347" s="5" t="inlineStr"/>
@@ -11728,7 +11728,7 @@
       </c>
       <c r="C348" s="7" t="inlineStr">
         <is>
-          <t>Wireless Room Sensor QAA2890/WI</t>
+          <t>Wireless Room Sensor QAA2150KT</t>
         </is>
       </c>
       <c r="D348" s="6" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="C349" s="5" t="inlineStr">
         <is>
-          <t>Wireless Room Sensor QFA2250KT</t>
+          <t>Wireless Room Sensor QAA2890/WI</t>
         </is>
       </c>
       <c r="D349" s="4" t="inlineStr">
@@ -11790,7 +11790,7 @@
       </c>
       <c r="C350" s="7" t="inlineStr">
         <is>
-          <t>Wireless Room Sensor QFA2890/WI</t>
+          <t>Wireless Room Sensor QFA2250KT</t>
         </is>
       </c>
       <c r="D350" s="6" t="inlineStr">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="C351" s="5" t="inlineStr">
         <is>
-          <t>Wireless Room Sensor QPA2350KT</t>
+          <t>Wireless Room Sensor QFA2890/WI</t>
         </is>
       </c>
       <c r="D351" s="4" t="inlineStr">
@@ -11852,7 +11852,7 @@
       </c>
       <c r="C352" s="7" t="inlineStr">
         <is>
-          <t>Wireless Room Sensor QPA2892/WI</t>
+          <t>Wireless Room Sensor QPA2350KT</t>
         </is>
       </c>
       <c r="D352" s="6" t="inlineStr">
@@ -11878,12 +11878,12 @@
       </c>
       <c r="B353" s="5" t="inlineStr">
         <is>
-          <t>Signify Netherlands B.V.</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C353" s="5" t="inlineStr">
         <is>
-          <t>Philips Hue Light</t>
+          <t>Wireless Room Sensor QPA2892/WI</t>
         </is>
       </c>
       <c r="D353" s="4" t="inlineStr">
@@ -11893,12 +11893,12 @@
       </c>
       <c r="E353" s="4" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F353" s="4" t="inlineStr">
         <is>
-          <t>Bulb</t>
+          <t>Temperature</t>
         </is>
       </c>
       <c r="G353" s="5" t="inlineStr"/>
@@ -11909,27 +11909,27 @@
       </c>
       <c r="B354" s="7" t="inlineStr">
         <is>
-          <t>Silicon Laboratories, Inc.</t>
+          <t>Signify Netherlands B.V.</t>
         </is>
       </c>
       <c r="C354" s="7" t="inlineStr">
         <is>
-          <t>MGM12P</t>
+          <t>Philips Hue Light</t>
         </is>
       </c>
       <c r="D354" s="6" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E354" s="6" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F354" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bulb</t>
         </is>
       </c>
       <c r="G354" s="7" t="inlineStr"/>
@@ -11945,7 +11945,7 @@
       </c>
       <c r="C355" s="5" t="inlineStr">
         <is>
-          <t>Silicon Labs Mighty Gecko (EFR32MG12x)</t>
+          <t>MGM12P</t>
         </is>
       </c>
       <c r="D355" s="4" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="E355" s="4" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="F355" s="4" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="C356" s="7" t="inlineStr">
         <is>
-          <t>Silicon Labs Mighty Gecko (EFR32MG13x)</t>
+          <t>Silicon Labs Mighty Gecko (EFR32MG12x)</t>
         </is>
       </c>
       <c r="D356" s="6" t="inlineStr">
@@ -12007,7 +12007,7 @@
       </c>
       <c r="C357" s="5" t="inlineStr">
         <is>
-          <t>Silicon Labs Mighty Gecko (EFR32MG21x)</t>
+          <t>Silicon Labs Mighty Gecko (EFR32MG13x)</t>
         </is>
       </c>
       <c r="D357" s="4" t="inlineStr">
@@ -12038,7 +12038,7 @@
       </c>
       <c r="C358" s="7" t="inlineStr">
         <is>
-          <t>Silicon Labs Mighty Gecko (EFR32MG24x)</t>
+          <t>Silicon Labs Mighty Gecko (EFR32MG21x)</t>
         </is>
       </c>
       <c r="D358" s="6" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="C359" s="5" t="inlineStr">
         <is>
-          <t>Silicon Labs Mighty Gecko (EFR32MG26x)</t>
+          <t>Silicon Labs Mighty Gecko (EFR32MG24x)</t>
         </is>
       </c>
       <c r="D359" s="4" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C360" s="7" t="inlineStr">
         <is>
-          <t>Silicon Labs Mighty Gecko (SiMG301)</t>
+          <t>Silicon Labs Mighty Gecko (EFR32MG26x)</t>
         </is>
       </c>
       <c r="D360" s="6" t="inlineStr">
@@ -12126,27 +12126,27 @@
       </c>
       <c r="B361" s="5" t="inlineStr">
         <is>
-          <t>Siterwell Electronics Co., Limited</t>
+          <t>Silicon Laboratories, Inc.</t>
         </is>
       </c>
       <c r="C361" s="5" t="inlineStr">
         <is>
-          <t>Smoke CO Alarm</t>
+          <t>Silicon Labs Mighty Gecko (SiMG301)</t>
         </is>
       </c>
       <c r="D361" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E361" s="4" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="F361" s="4" t="inlineStr">
         <is>
-          <t>Smoke alarm</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G361" s="5" t="inlineStr"/>
@@ -12157,12 +12157,12 @@
       </c>
       <c r="B362" s="7" t="inlineStr">
         <is>
-          <t>Skylux NV</t>
+          <t>Siterwell Electronics Co., Limited</t>
         </is>
       </c>
       <c r="C362" s="7" t="inlineStr">
         <is>
-          <t>Screen</t>
+          <t>Smoke CO Alarm</t>
         </is>
       </c>
       <c r="D362" s="6" t="inlineStr">
@@ -12172,12 +12172,12 @@
       </c>
       <c r="E362" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F362" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Smoke alarm</t>
         </is>
       </c>
       <c r="G362" s="7" t="inlineStr"/>
@@ -12193,7 +12193,7 @@
       </c>
       <c r="C363" s="5" t="inlineStr">
         <is>
-          <t>iWindow</t>
+          <t>Screen</t>
         </is>
       </c>
       <c r="D363" s="4" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="B364" s="7" t="inlineStr">
         <is>
-          <t>Sleekpoint Innovations Company Limited</t>
+          <t>Skylux NV</t>
         </is>
       </c>
       <c r="C364" s="7" t="inlineStr">
         <is>
-          <t>Airversa Purelle Smart Air Purifier</t>
+          <t>iWindow</t>
         </is>
       </c>
       <c r="D364" s="6" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="E364" s="6" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F364" s="6" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G364" s="7" t="inlineStr"/>
@@ -12255,7 +12255,7 @@
       </c>
       <c r="C365" s="5" t="inlineStr">
         <is>
-          <t>Button Controller</t>
+          <t>Airversa Purelle Smart Air Purifier</t>
         </is>
       </c>
       <c r="D365" s="4" t="inlineStr">
@@ -12265,12 +12265,12 @@
       </c>
       <c r="E365" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="F365" s="4" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="G365" s="5" t="inlineStr"/>
@@ -12286,7 +12286,7 @@
       </c>
       <c r="C366" s="7" t="inlineStr">
         <is>
-          <t>Smart Lock</t>
+          <t>Button Controller</t>
         </is>
       </c>
       <c r="D366" s="6" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="E366" s="6" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F366" s="6" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G366" s="7" t="inlineStr"/>
@@ -12312,12 +12312,12 @@
       </c>
       <c r="B367" s="5" t="inlineStr">
         <is>
-          <t>SmartWings Home LLC</t>
+          <t>Sleekpoint Innovations Company Limited</t>
         </is>
       </c>
       <c r="C367" s="5" t="inlineStr">
         <is>
-          <t>SmartWings window covering</t>
+          <t>Smart Lock</t>
         </is>
       </c>
       <c r="D367" s="4" t="inlineStr">
@@ -12327,12 +12327,12 @@
       </c>
       <c r="E367" s="4" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F367" s="4" t="inlineStr">
         <is>
-          <t>Blind</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="G367" s="5" t="inlineStr"/>
@@ -12343,12 +12343,12 @@
       </c>
       <c r="B368" s="7" t="inlineStr">
         <is>
-          <t>TETNET OÜ</t>
+          <t>SmartWings Home LLC</t>
         </is>
       </c>
       <c r="C368" s="7" t="inlineStr">
         <is>
-          <t>Tarken WM</t>
+          <t>SmartWings window covering</t>
         </is>
       </c>
       <c r="D368" s="6" t="inlineStr">
@@ -12363,7 +12363,7 @@
       </c>
       <c r="F368" s="6" t="inlineStr">
         <is>
-          <t>Window lock</t>
+          <t>Blind</t>
         </is>
       </c>
       <c r="G368" s="7" t="inlineStr"/>
@@ -12374,12 +12374,12 @@
       </c>
       <c r="B369" s="5" t="inlineStr">
         <is>
-          <t>Tedee Sp. z o.o.</t>
+          <t>TETNET OÜ</t>
         </is>
       </c>
       <c r="C369" s="5" t="inlineStr">
         <is>
-          <t>Tedee GO</t>
+          <t>Tarken WM</t>
         </is>
       </c>
       <c r="D369" s="4" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="E369" s="4" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="F369" s="4" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Window lock</t>
         </is>
       </c>
       <c r="G369" s="5" t="inlineStr"/>
@@ -12405,27 +12405,27 @@
       </c>
       <c r="B370" s="7" t="inlineStr">
         <is>
-          <t>Telink Semiconductor (Shanghai) Co., Ltd.</t>
+          <t>Tedee Sp. z o.o.</t>
         </is>
       </c>
       <c r="C370" s="7" t="inlineStr">
         <is>
-          <t>TL323X Series SoC</t>
+          <t>Tedee GO</t>
         </is>
       </c>
       <c r="D370" s="6" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E370" s="6" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F370" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="G370" s="7" t="inlineStr"/>
@@ -12441,7 +12441,7 @@
       </c>
       <c r="C371" s="5" t="inlineStr">
         <is>
-          <t>TLSR9</t>
+          <t>TL323X Series SoC</t>
         </is>
       </c>
       <c r="D371" s="4" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="C372" s="7" t="inlineStr">
         <is>
-          <t>TLSR9 - Border Router</t>
+          <t>TLSR9</t>
         </is>
       </c>
       <c r="D372" s="6" t="inlineStr">
@@ -12503,7 +12503,7 @@
       </c>
       <c r="C373" s="5" t="inlineStr">
         <is>
-          <t>TLSR922X Series SoC</t>
+          <t>TLSR9 - Border Router</t>
         </is>
       </c>
       <c r="D373" s="4" t="inlineStr">
@@ -12529,12 +12529,12 @@
       </c>
       <c r="B374" s="7" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc.</t>
+          <t>Telink Semiconductor (Shanghai) Co., Ltd.</t>
         </is>
       </c>
       <c r="C374" s="7" t="inlineStr">
         <is>
-          <t>CC2674x_1354x</t>
+          <t>TLSR922X Series SoC</t>
         </is>
       </c>
       <c r="D374" s="6" t="inlineStr">
@@ -12565,7 +12565,7 @@
       </c>
       <c r="C375" s="5" t="inlineStr">
         <is>
-          <t>CC26x2</t>
+          <t>CC2674x_1354x</t>
         </is>
       </c>
       <c r="D375" s="4" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="C376" s="7" t="inlineStr">
         <is>
-          <t>EOL - CC1352R/P</t>
+          <t>CC26x2</t>
         </is>
       </c>
       <c r="D376" s="6" t="inlineStr">
@@ -12622,27 +12622,27 @@
       </c>
       <c r="B377" s="5" t="inlineStr">
         <is>
-          <t>ThirdReality, Inc.</t>
+          <t>Texas Instruments Inc.</t>
         </is>
       </c>
       <c r="C377" s="5" t="inlineStr">
         <is>
-          <t>Smart Night Light-T</t>
+          <t>EOL - CC1352R/P</t>
         </is>
       </c>
       <c r="D377" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E377" s="4" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="F377" s="4" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G377" s="5" t="inlineStr"/>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="C378" s="7" t="inlineStr">
         <is>
-          <t>Smart Switch MT1</t>
+          <t>Smart Night Light-T</t>
         </is>
       </c>
       <c r="D378" s="6" t="inlineStr">
@@ -12673,7 +12673,7 @@
       </c>
       <c r="F378" s="6" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="G378" s="7" t="inlineStr"/>
@@ -12684,12 +12684,12 @@
       </c>
       <c r="B379" s="5" t="inlineStr">
         <is>
-          <t>Tuya Global Inc</t>
+          <t>ThirdReality, Inc.</t>
         </is>
       </c>
       <c r="C379" s="5" t="inlineStr">
         <is>
-          <t>Door Window Sensor</t>
+          <t>Smart Switch MT1</t>
         </is>
       </c>
       <c r="D379" s="4" t="inlineStr">
@@ -12699,12 +12699,12 @@
       </c>
       <c r="E379" s="4" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F379" s="4" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G379" s="5" t="inlineStr"/>
@@ -12720,7 +12720,7 @@
       </c>
       <c r="C380" s="7" t="inlineStr">
         <is>
-          <t>Motion Sensor</t>
+          <t>Door Window Sensor</t>
         </is>
       </c>
       <c r="D380" s="6" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="E380" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F380" s="6" t="inlineStr">
         <is>
-          <t>Presence</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="G380" s="7" t="inlineStr"/>
@@ -12751,7 +12751,7 @@
       </c>
       <c r="C381" s="5" t="inlineStr">
         <is>
-          <t>Smart Door Lock</t>
+          <t>Motion Sensor</t>
         </is>
       </c>
       <c r="D381" s="4" t="inlineStr">
@@ -12761,12 +12761,12 @@
       </c>
       <c r="E381" s="4" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F381" s="4" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Presence</t>
         </is>
       </c>
       <c r="G381" s="5" t="inlineStr"/>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C382" s="7" t="inlineStr">
         <is>
-          <t>Smart Window Covering</t>
+          <t>Smart Door Lock</t>
         </is>
       </c>
       <c r="D382" s="6" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E382" s="6" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F382" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="G382" s="7" t="inlineStr"/>
@@ -12813,17 +12813,17 @@
       </c>
       <c r="C383" s="5" t="inlineStr">
         <is>
-          <t>TS24-LC5</t>
+          <t>Smart Window Covering</t>
         </is>
       </c>
       <c r="D383" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E383" s="4" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="F383" s="4" t="inlineStr">
@@ -12844,7 +12844,7 @@
       </c>
       <c r="C384" s="7" t="inlineStr">
         <is>
-          <t>TS24-U</t>
+          <t>TS24-LC5</t>
         </is>
       </c>
       <c r="D384" s="6" t="inlineStr">
@@ -12875,7 +12875,7 @@
       </c>
       <c r="C385" s="5" t="inlineStr">
         <is>
-          <t>TS24-U-IPEX</t>
+          <t>TS24-U</t>
         </is>
       </c>
       <c r="D385" s="4" t="inlineStr">
@@ -12906,22 +12906,22 @@
       </c>
       <c r="C386" s="7" t="inlineStr">
         <is>
-          <t>Thread Bulb</t>
+          <t>TS24-U-IPEX</t>
         </is>
       </c>
       <c r="D386" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E386" s="6" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="F386" s="6" t="inlineStr">
         <is>
-          <t>Bulb</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G386" s="7" t="inlineStr"/>
@@ -12937,7 +12937,7 @@
       </c>
       <c r="C387" s="5" t="inlineStr">
         <is>
-          <t>Thread Color Temperature Light Drive</t>
+          <t>Thread Bulb</t>
         </is>
       </c>
       <c r="D387" s="4" t="inlineStr">
@@ -12952,7 +12952,7 @@
       </c>
       <c r="F387" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bulb</t>
         </is>
       </c>
       <c r="G387" s="5" t="inlineStr"/>
@@ -12968,7 +12968,7 @@
       </c>
       <c r="C388" s="7" t="inlineStr">
         <is>
-          <t>Thread Dimmable Light Drive</t>
+          <t>Thread Color Temperature Light Drive</t>
         </is>
       </c>
       <c r="D388" s="6" t="inlineStr">
@@ -12994,12 +12994,12 @@
       </c>
       <c r="B389" s="5" t="inlineStr">
         <is>
-          <t>Vitrumshade LLC</t>
+          <t>Tuya Global Inc</t>
         </is>
       </c>
       <c r="C389" s="5" t="inlineStr">
         <is>
-          <t>Smart Internal Blinds</t>
+          <t>Thread Dimmable Light Drive</t>
         </is>
       </c>
       <c r="D389" s="4" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E389" s="4" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F389" s="4" t="inlineStr">
         <is>
-          <t>Blind</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G389" s="5" t="inlineStr"/>
@@ -13025,12 +13025,12 @@
       </c>
       <c r="B390" s="7" t="inlineStr">
         <is>
-          <t>WAREMA Renkhoff SE</t>
+          <t>Vitrumshade LLC</t>
         </is>
       </c>
       <c r="C390" s="7" t="inlineStr">
         <is>
-          <t>Xeenos Go Aktor Jalousie Plug</t>
+          <t>Smart Internal Blinds</t>
         </is>
       </c>
       <c r="D390" s="6" t="inlineStr">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="C391" s="5" t="inlineStr">
         <is>
-          <t>Xeenos Go Aktor Jalousie UP</t>
+          <t>Xeenos Go Aktor Jalousie Plug</t>
         </is>
       </c>
       <c r="D391" s="4" t="inlineStr">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="C392" s="7" t="inlineStr">
         <is>
-          <t>Xeenos Go Aktor Rollladen Plug</t>
+          <t>Xeenos Go Aktor Jalousie UP</t>
         </is>
       </c>
       <c r="D392" s="6" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="C393" s="5" t="inlineStr">
         <is>
-          <t>Xeenos Go Aktor Rollladen UP</t>
+          <t>Xeenos Go Aktor Rollladen Plug</t>
         </is>
       </c>
       <c r="D393" s="4" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F393" s="4" t="inlineStr">
         <is>
-          <t>Shutter</t>
+          <t>Blind</t>
         </is>
       </c>
       <c r="G393" s="5" t="inlineStr"/>
@@ -13154,7 +13154,7 @@
       </c>
       <c r="C394" s="7" t="inlineStr">
         <is>
-          <t>Xeenos Go Aktor Switch 2K UP</t>
+          <t>Xeenos Go Aktor Rollladen UP</t>
         </is>
       </c>
       <c r="D394" s="6" t="inlineStr">
@@ -13164,12 +13164,12 @@
       </c>
       <c r="E394" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="F394" s="6" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Shutter</t>
         </is>
       </c>
       <c r="G394" s="7" t="inlineStr"/>
@@ -13180,12 +13180,12 @@
       </c>
       <c r="B395" s="5" t="inlineStr">
         <is>
-          <t>WINTECKOREA INC</t>
+          <t>WAREMA Renkhoff SE</t>
         </is>
       </c>
       <c r="C395" s="5" t="inlineStr">
         <is>
-          <t>GATEWAY-MT</t>
+          <t>Xeenos Go Aktor Switch 2K UP</t>
         </is>
       </c>
       <c r="D395" s="4" t="inlineStr">
@@ -13195,12 +13195,12 @@
       </c>
       <c r="E395" s="4" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F395" s="4" t="inlineStr">
         <is>
-          <t>Blind</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G395" s="5" t="inlineStr"/>
@@ -13211,12 +13211,12 @@
       </c>
       <c r="B396" s="7" t="inlineStr">
         <is>
-          <t>WNC Corporation</t>
+          <t>WINTECKOREA INC</t>
         </is>
       </c>
       <c r="C396" s="7" t="inlineStr">
         <is>
-          <t>Indoor Air Quality Monitor</t>
+          <t>GATEWAY-MT</t>
         </is>
       </c>
       <c r="D396" s="6" t="inlineStr">
@@ -13226,12 +13226,12 @@
       </c>
       <c r="E396" s="6" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="F396" s="6" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Blind</t>
         </is>
       </c>
       <c r="G396" s="7" t="inlineStr"/>
@@ -13242,12 +13242,12 @@
       </c>
       <c r="B397" s="5" t="inlineStr">
         <is>
-          <t>Watts Water Technologies</t>
+          <t>WNC Corporation</t>
         </is>
       </c>
       <c r="C397" s="5" t="inlineStr">
         <is>
-          <t>Tekmar Smart Steam Control 289</t>
+          <t>Indoor Air Quality Monitor</t>
         </is>
       </c>
       <c r="D397" s="4" t="inlineStr">
@@ -13257,12 +13257,12 @@
       </c>
       <c r="E397" s="4" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F397" s="4" t="inlineStr">
         <is>
-          <t>Heating</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="G397" s="5" t="inlineStr"/>
@@ -13278,7 +13278,7 @@
       </c>
       <c r="C398" s="7" t="inlineStr">
         <is>
-          <t>tekmar Smart Boiler Control 294</t>
+          <t>Tekmar Smart Steam Control 289</t>
         </is>
       </c>
       <c r="D398" s="6" t="inlineStr">
@@ -13309,7 +13309,7 @@
       </c>
       <c r="C399" s="5" t="inlineStr">
         <is>
-          <t>tekmar Wireless Mesh Indoor Sensor 042</t>
+          <t>tekmar Smart Boiler Control 294</t>
         </is>
       </c>
       <c r="D399" s="4" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="E399" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="F399" s="4" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>Heating</t>
         </is>
       </c>
       <c r="G399" s="5" t="inlineStr"/>
@@ -13340,7 +13340,7 @@
       </c>
       <c r="C400" s="7" t="inlineStr">
         <is>
-          <t>tekmar Wireless Mesh Outdoor Sensor 043</t>
+          <t>tekmar Wireless Mesh Indoor Sensor 042</t>
         </is>
       </c>
       <c r="D400" s="6" t="inlineStr">
@@ -13350,7 +13350,7 @@
       </c>
       <c r="E400" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F400" s="6" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="B401" s="5" t="inlineStr">
         <is>
-          <t>What's Matter Inc.</t>
+          <t>Watts Water Technologies</t>
         </is>
       </c>
       <c r="C401" s="5" t="inlineStr">
         <is>
-          <t>Air Quality Sensor</t>
+          <t>tekmar Wireless Mesh Outdoor Sensor 043</t>
         </is>
       </c>
       <c r="D401" s="4" t="inlineStr">
@@ -13381,12 +13381,12 @@
       </c>
       <c r="E401" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F401" s="4" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Temperature</t>
         </is>
       </c>
       <c r="G401" s="5" t="inlineStr"/>
@@ -13402,7 +13402,7 @@
       </c>
       <c r="C402" s="7" t="inlineStr">
         <is>
-          <t>Light Sensor</t>
+          <t>Air Quality Sensor</t>
         </is>
       </c>
       <c r="D402" s="6" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="E402" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F402" s="6" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="G402" s="7" t="inlineStr"/>
@@ -13433,7 +13433,7 @@
       </c>
       <c r="C403" s="5" t="inlineStr">
         <is>
-          <t>Radar Presence Sensor</t>
+          <t>Light Sensor</t>
         </is>
       </c>
       <c r="D403" s="4" t="inlineStr">
@@ -13443,12 +13443,12 @@
       </c>
       <c r="E403" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F403" s="4" t="inlineStr">
         <is>
-          <t>Presence</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="G403" s="5" t="inlineStr"/>
@@ -13464,22 +13464,22 @@
       </c>
       <c r="C404" s="7" t="inlineStr">
         <is>
-          <t>Smoke Sensor</t>
+          <t>Radar Presence Sensor</t>
         </is>
       </c>
       <c r="D404" s="6" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E404" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F404" s="6" t="inlineStr">
         <is>
-          <t>Smoke alarm</t>
+          <t>Presence</t>
         </is>
       </c>
       <c r="G404" s="7" t="inlineStr"/>
@@ -13495,22 +13495,22 @@
       </c>
       <c r="C405" s="5" t="inlineStr">
         <is>
-          <t>Temperature and Humidity Sensor</t>
+          <t>Smoke Sensor</t>
         </is>
       </c>
       <c r="D405" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E405" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F405" s="4" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>Smoke alarm</t>
         </is>
       </c>
       <c r="G405" s="5" t="inlineStr"/>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C406" s="7" t="inlineStr">
         <is>
-          <t>Vibration Sensor</t>
+          <t>Temperature and Humidity Sensor</t>
         </is>
       </c>
       <c r="D406" s="6" t="inlineStr">
@@ -13536,12 +13536,12 @@
       </c>
       <c r="E406" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F406" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Temperature</t>
         </is>
       </c>
       <c r="G406" s="7" t="inlineStr"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="C407" s="5" t="inlineStr">
         <is>
-          <t>Window and Door Sensor</t>
+          <t>Vibration Sensor</t>
         </is>
       </c>
       <c r="D407" s="4" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="E407" s="4" t="inlineStr">
         <is>
+          <t>Sensor</t>
+        </is>
+      </c>
+      <c r="F407" s="4" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="F407" s="4" t="inlineStr">
-        <is>
-          <t>Contact</t>
         </is>
       </c>
       <c r="G407" s="5" t="inlineStr"/>
@@ -13583,12 +13583,12 @@
       </c>
       <c r="B408" s="7" t="inlineStr">
         <is>
-          <t>WideSky.cloud Pty. Ltd</t>
+          <t>What's Matter Inc.</t>
         </is>
       </c>
       <c r="C408" s="7" t="inlineStr">
         <is>
-          <t>WideSky Hub</t>
+          <t>Window and Door Sensor</t>
         </is>
       </c>
       <c r="D408" s="6" t="inlineStr">
@@ -13598,12 +13598,12 @@
       </c>
       <c r="E408" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F408" s="6" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="G408" s="7" t="inlineStr"/>
@@ -13614,12 +13614,12 @@
       </c>
       <c r="B409" s="5" t="inlineStr">
         <is>
-          <t>Xiaomi Communications Co., Ltd.</t>
+          <t>WideSky.cloud Pty. Ltd</t>
         </is>
       </c>
       <c r="C409" s="5" t="inlineStr">
         <is>
-          <t>Xiaomi Self-Install Smart Lock (Keypad Included)</t>
+          <t>WideSky Hub</t>
         </is>
       </c>
       <c r="D409" s="4" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="E409" s="4" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F409" s="4" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G409" s="5" t="inlineStr"/>
@@ -13645,12 +13645,12 @@
       </c>
       <c r="B410" s="7" t="inlineStr">
         <is>
-          <t>Xthings Industry</t>
+          <t>Xiaomi Communications Co., Ltd.</t>
         </is>
       </c>
       <c r="C410" s="7" t="inlineStr">
         <is>
-          <t>ULTRALOQ Bolt Fingerprint and NFC Smart Matter Deadbolt</t>
+          <t>Xiaomi Self-Install Smart Lock (Keypad Included)</t>
         </is>
       </c>
       <c r="D410" s="6" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="C411" s="5" t="inlineStr">
         <is>
-          <t>ULTRALOQ Bolt NFC Smart Matter Deadbolt</t>
+          <t>ULTRALOQ Bolt Fingerprint and NFC Smart Matter Deadbolt</t>
         </is>
       </c>
       <c r="D411" s="4" t="inlineStr">
@@ -13712,7 +13712,7 @@
       </c>
       <c r="C412" s="7" t="inlineStr">
         <is>
-          <t>ULTRALOQ Latch5 Fingerprint Smart Matter Lever</t>
+          <t>ULTRALOQ Bolt NFC Smart Matter Deadbolt</t>
         </is>
       </c>
       <c r="D412" s="6" t="inlineStr">
@@ -13743,7 +13743,7 @@
       </c>
       <c r="C413" s="5" t="inlineStr">
         <is>
-          <t>ULTRALOQ U-Bolt Pro Smart Matter Deadbolt</t>
+          <t>ULTRALOQ Latch5 Fingerprint Smart Matter Lever</t>
         </is>
       </c>
       <c r="D413" s="4" t="inlineStr">
@@ -13774,7 +13774,7 @@
       </c>
       <c r="C414" s="7" t="inlineStr">
         <is>
-          <t>ULTRALOQ U-bolt Smart Matter Deadbolt</t>
+          <t>ULTRALOQ U-Bolt Pro Smart Matter Deadbolt</t>
         </is>
       </c>
       <c r="D414" s="6" t="inlineStr">
@@ -13805,7 +13805,7 @@
       </c>
       <c r="C415" s="5" t="inlineStr">
         <is>
-          <t>Ultraloq Bolt Fingerprint Smart Matter Deadbolt</t>
+          <t>ULTRALOQ U-bolt Smart Matter Deadbolt</t>
         </is>
       </c>
       <c r="D415" s="4" t="inlineStr">
@@ -13831,12 +13831,12 @@
       </c>
       <c r="B416" s="7" t="inlineStr">
         <is>
-          <t>Zemismart Technology Limited</t>
+          <t>Xthings Industry</t>
         </is>
       </c>
       <c r="C416" s="7" t="inlineStr">
         <is>
-          <t>Zemismart Lighting Kit</t>
+          <t>Ultraloq Bolt Fingerprint Smart Matter Deadbolt</t>
         </is>
       </c>
       <c r="D416" s="6" t="inlineStr">
@@ -13846,12 +13846,12 @@
       </c>
       <c r="E416" s="6" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F416" s="6" t="inlineStr">
         <is>
-          <t>Lightstrip</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="G416" s="7" t="inlineStr"/>
@@ -13867,7 +13867,7 @@
       </c>
       <c r="C417" s="5" t="inlineStr">
         <is>
-          <t>Zemismart MT01 Slide Curtain</t>
+          <t>Zemismart Lighting Kit</t>
         </is>
       </c>
       <c r="D417" s="4" t="inlineStr">
@@ -13877,12 +13877,12 @@
       </c>
       <c r="E417" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F417" s="4" t="inlineStr">
         <is>
-          <t>Curtain</t>
+          <t>Lightstrip</t>
         </is>
       </c>
       <c r="G417" s="5" t="inlineStr"/>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="C418" s="7" t="inlineStr">
         <is>
-          <t>Zemismart Motion Detector</t>
+          <t>Zemismart MT01 Slide Curtain</t>
         </is>
       </c>
       <c r="D418" s="6" t="inlineStr">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="F418" s="6" t="inlineStr">
         <is>
-          <t>Presence</t>
+          <t>Curtain</t>
         </is>
       </c>
       <c r="G418" s="7" t="inlineStr"/>
@@ -13929,7 +13929,7 @@
       </c>
       <c r="C419" s="5" t="inlineStr">
         <is>
-          <t>Zemismart Thread Curtain Motor</t>
+          <t>Zemismart Motion Detector</t>
         </is>
       </c>
       <c r="D419" s="4" t="inlineStr">
@@ -13939,12 +13939,12 @@
       </c>
       <c r="E419" s="4" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F419" s="4" t="inlineStr">
         <is>
-          <t>Curtain</t>
+          <t>Presence</t>
         </is>
       </c>
       <c r="G419" s="5" t="inlineStr"/>
@@ -13960,7 +13960,7 @@
       </c>
       <c r="C420" s="7" t="inlineStr">
         <is>
-          <t>Zemismart Window Shading System Driver</t>
+          <t>Zemismart Thread Curtain Motor</t>
         </is>
       </c>
       <c r="D420" s="6" t="inlineStr">
@@ -13986,12 +13986,12 @@
       </c>
       <c r="B421" s="5" t="inlineStr">
         <is>
-          <t>Zhejiang General light Curtain Co., Ltd.</t>
+          <t>Zemismart Technology Limited</t>
         </is>
       </c>
       <c r="C421" s="5" t="inlineStr">
         <is>
-          <t>25 DC roller shutter motor</t>
+          <t>Zemismart Window Shading System Driver</t>
         </is>
       </c>
       <c r="D421" s="4" t="inlineStr">
@@ -14006,7 +14006,7 @@
       </c>
       <c r="F421" s="4" t="inlineStr">
         <is>
-          <t>Blind</t>
+          <t>Curtain</t>
         </is>
       </c>
       <c r="G421" s="5" t="inlineStr"/>
@@ -14017,12 +14017,12 @@
       </c>
       <c r="B422" s="7" t="inlineStr">
         <is>
-          <t>Zhejiang Jiecang Linear Motion Technology Co.,Ltd</t>
+          <t>Zhejiang General light Curtain Co., Ltd.</t>
         </is>
       </c>
       <c r="C422" s="7" t="inlineStr">
         <is>
-          <t>Matter 1.3 Window covering</t>
+          <t>25 DC roller shutter motor</t>
         </is>
       </c>
       <c r="D422" s="6" t="inlineStr">
@@ -14048,12 +14048,12 @@
       </c>
       <c r="B423" s="5" t="inlineStr">
         <is>
-          <t>Zhejiang Moorgen Group Co., Ltd.</t>
+          <t>Zhejiang Jiecang Linear Motion Technology Co.,Ltd</t>
         </is>
       </c>
       <c r="C423" s="5" t="inlineStr">
         <is>
-          <t>Crystal Series Rechargeable Lamp</t>
+          <t>Matter 1.3 Window covering</t>
         </is>
       </c>
       <c r="D423" s="4" t="inlineStr">
@@ -14063,12 +14063,12 @@
       </c>
       <c r="E423" s="4" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="F423" s="4" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Blind</t>
         </is>
       </c>
       <c r="G423" s="5" t="inlineStr"/>
@@ -14079,12 +14079,12 @@
       </c>
       <c r="B424" s="7" t="inlineStr">
         <is>
-          <t>Zhuhai Ltech Technology Co., Ltd</t>
+          <t>Zhejiang Moorgen Group Co., Ltd.</t>
         </is>
       </c>
       <c r="C424" s="7" t="inlineStr">
         <is>
-          <t>Ltech Constant Current LED Driver (LA series)</t>
+          <t>Crystal Series Rechargeable Lamp</t>
         </is>
       </c>
       <c r="D424" s="6" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="F424" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="G424" s="7" t="inlineStr"/>
@@ -14115,7 +14115,7 @@
       </c>
       <c r="C425" s="5" t="inlineStr">
         <is>
-          <t>Ltech Constant Current LED Driver (SE series)</t>
+          <t>Ltech Constant Current LED Driver (LA series)</t>
         </is>
       </c>
       <c r="D425" s="4" t="inlineStr">
@@ -14146,7 +14146,7 @@
       </c>
       <c r="C426" s="7" t="inlineStr">
         <is>
-          <t>Ltech Constant Voltage LED Driver (LM, LA, HMA series)</t>
+          <t>Ltech Constant Current LED Driver (SE series)</t>
         </is>
       </c>
       <c r="D426" s="6" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="C427" s="5" t="inlineStr">
         <is>
-          <t>Ltech Constant Voltage LED Driver (MA series)</t>
+          <t>Ltech Constant Voltage LED Driver (LM, LA, HMA series)</t>
         </is>
       </c>
       <c r="D427" s="4" t="inlineStr">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="C428" s="7" t="inlineStr">
         <is>
-          <t>Ltech Light Converter (E6, CG, KM families)</t>
+          <t>Ltech Constant Voltage LED Driver (MA series)</t>
         </is>
       </c>
       <c r="D428" s="6" t="inlineStr">
@@ -14223,7 +14223,7 @@
       </c>
       <c r="F428" s="6" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G428" s="7" t="inlineStr"/>
@@ -14239,7 +14239,7 @@
       </c>
       <c r="C429" s="5" t="inlineStr">
         <is>
-          <t>Ltech On/Off Light Driver</t>
+          <t>Ltech Light Converter (E6, CG, KM families)</t>
         </is>
       </c>
       <c r="D429" s="4" t="inlineStr">
@@ -14265,12 +14265,12 @@
       </c>
       <c r="B430" s="7" t="inlineStr">
         <is>
-          <t>Zumtobel Group AG</t>
+          <t>Zhuhai Ltech Technology Co., Ltd</t>
         </is>
       </c>
       <c r="C430" s="7" t="inlineStr">
         <is>
-          <t>Driver LC 100W 24V MTR SC PRE2</t>
+          <t>Ltech On/Off Light Driver</t>
         </is>
       </c>
       <c r="D430" s="6" t="inlineStr">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="F430" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G430" s="7" t="inlineStr"/>
@@ -14301,7 +14301,7 @@
       </c>
       <c r="C431" s="5" t="inlineStr">
         <is>
-          <t>Driver LC 150W 24V MTR SC PRE2</t>
+          <t>Driver LC 100W 24V MTR SC PRE2</t>
         </is>
       </c>
       <c r="D431" s="4" t="inlineStr">
@@ -14332,7 +14332,7 @@
       </c>
       <c r="C432" s="7" t="inlineStr">
         <is>
-          <t>Driver LC 35W 24V MTR SC PRE2</t>
+          <t>Driver LC 150W 24V MTR SC PRE2</t>
         </is>
       </c>
       <c r="D432" s="6" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="C433" s="5" t="inlineStr">
         <is>
-          <t>Driver LC 60W 24V MTR SC PRE2</t>
+          <t>Driver LC 35W 24V MTR SC PRE2</t>
         </is>
       </c>
       <c r="D433" s="4" t="inlineStr">
@@ -14394,7 +14394,7 @@
       </c>
       <c r="C434" s="7" t="inlineStr">
         <is>
-          <t>Wireless Module MTR</t>
+          <t>Driver LC 60W 24V MTR SC PRE2</t>
         </is>
       </c>
       <c r="D434" s="6" t="inlineStr">
@@ -14425,7 +14425,7 @@
       </c>
       <c r="C435" s="5" t="inlineStr">
         <is>
-          <t>Wireless Module SR MTR</t>
+          <t>Wireless Module MTR</t>
         </is>
       </c>
       <c r="D435" s="4" t="inlineStr">
@@ -14456,7 +14456,7 @@
       </c>
       <c r="C436" s="7" t="inlineStr">
         <is>
-          <t>Wireless module passive MTR</t>
+          <t>Wireless Module SR MTR</t>
         </is>
       </c>
       <c r="D436" s="6" t="inlineStr">
@@ -14471,7 +14471,7 @@
       </c>
       <c r="F436" s="6" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G436" s="7" t="inlineStr"/>
@@ -14482,12 +14482,12 @@
       </c>
       <c r="B437" s="5" t="inlineStr">
         <is>
-          <t>geo</t>
+          <t>Zumtobel Group AG</t>
         </is>
       </c>
       <c r="C437" s="5" t="inlineStr">
         <is>
-          <t>geo SeeZero Display</t>
+          <t>Wireless module passive MTR</t>
         </is>
       </c>
       <c r="D437" s="4" t="inlineStr">
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E437" s="4" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F437" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G437" s="5" t="inlineStr"/>
@@ -14518,7 +14518,7 @@
       </c>
       <c r="C438" s="7" t="inlineStr">
         <is>
-          <t>geo SeeZero Heating Controller</t>
+          <t>geo SeeZero Display</t>
         </is>
       </c>
       <c r="D438" s="6" t="inlineStr">
@@ -14544,22 +14544,22 @@
       </c>
       <c r="B439" s="5" t="inlineStr">
         <is>
-          <t>synaptics</t>
+          <t>geo</t>
         </is>
       </c>
       <c r="C439" s="5" t="inlineStr">
         <is>
-          <t>SYN4384 (as Thread RCP) + [Synaptics Linux host base on Raspberry Pi 4] Border Router</t>
+          <t>geo SeeZero Heating Controller</t>
         </is>
       </c>
       <c r="D439" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E439" s="4" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="F439" s="4" t="inlineStr">
@@ -14580,7 +14580,7 @@
       </c>
       <c r="C440" s="7" t="inlineStr">
         <is>
-          <t>Synaptics V1.3 Border Router Assembly - SYN20708 (as Thread RCP) + Linux Host</t>
+          <t>SYN4384 (as Thread RCP) + [Synaptics Linux host base on Raspberry Pi 4] Border Router</t>
         </is>
       </c>
       <c r="D440" s="6" t="inlineStr">
@@ -14590,7 +14590,7 @@
       </c>
       <c r="E440" s="6" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="F440" s="6" t="inlineStr">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="C441" s="5" t="inlineStr">
         <is>
-          <t>Synaptics V1.4 Border Router Assembly - SYN20708 (as Thread RCP) + Raspberry Pi Linux host</t>
+          <t>Synaptics V1.3 Border Router Assembly - SYN20708 (as Thread RCP) + Linux Host</t>
         </is>
       </c>
       <c r="D441" s="4" t="inlineStr">
@@ -14637,12 +14637,12 @@
       </c>
       <c r="B442" s="7" t="inlineStr">
         <is>
-          <t>tado</t>
+          <t>synaptics</t>
         </is>
       </c>
       <c r="C442" s="7" t="inlineStr">
         <is>
-          <t>Heat Pump Optimizer</t>
+          <t>Synaptics V1.4 Border Router Assembly - SYN20708 (as Thread RCP) + Raspberry Pi Linux host</t>
         </is>
       </c>
       <c r="D442" s="6" t="inlineStr">
@@ -14652,12 +14652,12 @@
       </c>
       <c r="E442" s="6" t="inlineStr">
         <is>
+          <t>Chipset</t>
+        </is>
+      </c>
+      <c r="F442" s="6" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="F442" s="6" t="inlineStr">
-        <is>
-          <t>Heating</t>
         </is>
       </c>
       <c r="G442" s="7" t="inlineStr"/>
@@ -14673,7 +14673,7 @@
       </c>
       <c r="C443" s="5" t="inlineStr">
         <is>
-          <t>Internet Bridge X</t>
+          <t>Heat Pump Optimizer</t>
         </is>
       </c>
       <c r="D443" s="4" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="E443" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F443" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Heating</t>
         </is>
       </c>
       <c r="G443" s="5" t="inlineStr"/>
@@ -14704,22 +14704,22 @@
       </c>
       <c r="C444" s="7" t="inlineStr">
         <is>
-          <t>Smart Radiator Thermostat X</t>
+          <t>Internet Bridge X</t>
         </is>
       </c>
       <c r="D444" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E444" s="6" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F444" s="6" t="inlineStr">
         <is>
-          <t>Heating</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G444" s="7" t="inlineStr"/>
@@ -14766,7 +14766,7 @@
       </c>
       <c r="C446" s="7" t="inlineStr">
         <is>
-          <t>Smart Thermostat X</t>
+          <t>Smart Radiator Thermostat X</t>
         </is>
       </c>
       <c r="D446" s="6" t="inlineStr">
@@ -14776,7 +14776,7 @@
       </c>
       <c r="E446" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="F446" s="6" t="inlineStr">
@@ -14797,7 +14797,7 @@
       </c>
       <c r="C447" s="5" t="inlineStr">
         <is>
-          <t>Smart Thermostat X Gen 2</t>
+          <t>Smart Thermostat X</t>
         </is>
       </c>
       <c r="D447" s="4" t="inlineStr">
@@ -14807,7 +14807,7 @@
       </c>
       <c r="E447" s="4" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F447" s="4" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="C448" s="7" t="inlineStr">
         <is>
-          <t>Wireless Receiver X</t>
+          <t>Smart Thermostat X Gen 2</t>
         </is>
       </c>
       <c r="D448" s="6" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E448" s="6" t="inlineStr">
@@ -14859,7 +14859,7 @@
       </c>
       <c r="C449" s="5" t="inlineStr">
         <is>
-          <t>Wireless Receiver X - Programmer with Hot Water Control and OpenTherm</t>
+          <t>Wireless Receiver X</t>
         </is>
       </c>
       <c r="D449" s="4" t="inlineStr">
@@ -14890,22 +14890,22 @@
       </c>
       <c r="C450" s="7" t="inlineStr">
         <is>
-          <t>Wireless Temperature Sensor X</t>
+          <t>Wireless Receiver X - Programmer with Hot Water Control and OpenTherm</t>
         </is>
       </c>
       <c r="D450" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E450" s="6" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="F450" s="6" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>Heating</t>
         </is>
       </c>
       <c r="G450" s="7" t="inlineStr"/>
@@ -14921,31 +14921,62 @@
       </c>
       <c r="C451" s="5" t="inlineStr">
         <is>
+          <t>Wireless Temperature Sensor X</t>
+        </is>
+      </c>
+      <c r="D451" s="4" t="inlineStr">
+        <is>
+          <t>Built on Thread</t>
+        </is>
+      </c>
+      <c r="E451" s="4" t="inlineStr">
+        <is>
+          <t>Sensor</t>
+        </is>
+      </c>
+      <c r="F451" s="4" t="inlineStr">
+        <is>
+          <t>Temperature</t>
+        </is>
+      </c>
+      <c r="G451" s="5" t="inlineStr"/>
+    </row>
+    <row r="452" ht="18" customHeight="1">
+      <c r="A452" s="6" t="n">
+        <v>448</v>
+      </c>
+      <c r="B452" s="7" t="inlineStr">
+        <is>
+          <t>tado</t>
+        </is>
+      </c>
+      <c r="C452" s="7" t="inlineStr">
+        <is>
           <t>Wireless Temperature Sensor X Gen 2</t>
         </is>
       </c>
-      <c r="D451" s="4" t="inlineStr">
-        <is>
-          <t>Built on Thread</t>
-        </is>
-      </c>
-      <c r="E451" s="4" t="inlineStr">
+      <c r="D452" s="6" t="inlineStr">
+        <is>
+          <t>Built on Thread</t>
+        </is>
+      </c>
+      <c r="E452" s="6" t="inlineStr">
         <is>
           <t>Sensor</t>
         </is>
       </c>
-      <c r="F451" s="4" t="inlineStr">
+      <c r="F452" s="6" t="inlineStr">
         <is>
           <t>Temperature</t>
         </is>
       </c>
-      <c r="G451" s="5" t="inlineStr"/>
+      <c r="G452" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G451"/>
+  <autoFilter ref="A4:G452"/>
   <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14957,7 +14988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F131"/>
+  <dimension ref="A1:F132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -15263,7 +15294,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -15313,7 +15344,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>HVAC, Sensor</t>
+          <t>HVAC, Infrastructure, Sensor</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -15363,7 +15394,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Infrastructure, Lighting</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -15388,7 +15419,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Infrastructure, Sensor</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -15438,7 +15469,7 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -15713,7 +15744,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Lighting, Window covering</t>
+          <t>Lighting, Sensor, Window covering</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -15938,7 +15969,7 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>HVAC, Sensor</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
@@ -16463,7 +16494,7 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Automation control, Lighting</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -16588,7 +16619,7 @@
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
@@ -17305,7 +17336,7 @@
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>HUZHOU DOORMA INTEL TECH CO LTD</t>
+          <t>Grimsholm Products AB</t>
         </is>
       </c>
       <c r="B96" s="4" t="n">
@@ -17313,12 +17344,12 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Curtain</t>
+          <t>Irrigation</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -17330,7 +17361,7 @@
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>Hinkley Lighting Inc.</t>
+          <t>HUZHOU DOORMA INTEL TECH CO LTD</t>
         </is>
       </c>
       <c r="B97" s="6" t="n">
@@ -17338,12 +17369,12 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Curtain</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
@@ -17355,7 +17386,7 @@
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Insta GmbH</t>
+          <t>Hinkley Lighting Inc.</t>
         </is>
       </c>
       <c r="B98" s="4" t="n">
@@ -17363,12 +17394,12 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -17380,7 +17411,7 @@
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>LOCKIN (U.S.) INC.</t>
+          <t>Insta GmbH</t>
         </is>
       </c>
       <c r="B99" s="6" t="n">
@@ -17388,12 +17419,12 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
@@ -17405,7 +17436,7 @@
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>LOCKIN (U.S.) INC.</t>
         </is>
       </c>
       <c r="B100" s="4" t="n">
@@ -17413,12 +17444,12 @@
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -17430,7 +17461,7 @@
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>Level Home Inc.</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="B101" s="6" t="n">
@@ -17438,12 +17469,12 @@
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
@@ -17455,7 +17486,7 @@
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>MEAN WELL ENTERPRISES CO., LTD.</t>
+          <t>Level Home Inc.</t>
         </is>
       </c>
       <c r="B102" s="4" t="n">
@@ -17463,12 +17494,12 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -17480,7 +17511,7 @@
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>MIWA LOCK Co., LTD.</t>
+          <t>MEAN WELL ENTERPRISES CO., LTD.</t>
         </is>
       </c>
       <c r="B103" s="6" t="n">
@@ -17488,12 +17519,12 @@
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
@@ -17505,7 +17536,7 @@
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>MMB Networks</t>
+          <t>MIWA LOCK Co., LTD.</t>
         </is>
       </c>
       <c r="B104" s="4" t="n">
@@ -17513,12 +17544,12 @@
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -17530,7 +17561,7 @@
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>Mediola connected living AG</t>
+          <t>MMB Networks</t>
         </is>
       </c>
       <c r="B105" s="6" t="n">
@@ -17538,24 +17569,24 @@
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Mighton Products Ltd</t>
+          <t>Mediola connected living AG</t>
         </is>
       </c>
       <c r="B106" s="4" t="n">
@@ -17563,24 +17594,24 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>Mikrotikls SIA</t>
+          <t>Mighton Products Ltd</t>
         </is>
       </c>
       <c r="B107" s="6" t="n">
@@ -17588,12 +17619,12 @@
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
@@ -17605,7 +17636,7 @@
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>NAMI AI</t>
+          <t>Mikrotikls SIA</t>
         </is>
       </c>
       <c r="B108" s="4" t="n">
@@ -17613,24 +17644,24 @@
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>Smart plug</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>Ningbo Dooya Mechanic &amp; Electronic Technology Co., Ltd</t>
+          <t>NAMI AI</t>
         </is>
       </c>
       <c r="B109" s="6" t="n">
@@ -17638,24 +17669,24 @@
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>Blind</t>
+          <t>Smart plug</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>ORANGE</t>
+          <t>Ningbo Dooya Mechanic &amp; Electronic Technology Co., Ltd</t>
         </is>
       </c>
       <c r="B110" s="4" t="n">
@@ -17663,24 +17694,24 @@
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Wi-Fi Access Point</t>
+          <t>Blind</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>Qualcomm Inc.</t>
+          <t>ORANGE</t>
         </is>
       </c>
       <c r="B111" s="6" t="n">
@@ -17688,12 +17719,12 @@
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Wi-Fi Access Point</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
@@ -17705,7 +17736,7 @@
     <row r="112" ht="20" customHeight="1">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Quectel Wireless Solutions Co., Ltd.</t>
+          <t>Qualcomm Inc.</t>
         </is>
       </c>
       <c r="B112" s="4" t="n">
@@ -17713,7 +17744,7 @@
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
@@ -17730,7 +17761,7 @@
     <row r="113" ht="20" customHeight="1">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>SENSEREO LIMITED</t>
+          <t>Quectel Wireless Solutions Co., Ltd.</t>
         </is>
       </c>
       <c r="B113" s="6" t="n">
@@ -17738,24 +17769,24 @@
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>Smoke alarm</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>Savant</t>
+          <t>SENSEREO LIMITED</t>
         </is>
       </c>
       <c r="B114" s="4" t="n">
@@ -17763,12 +17794,12 @@
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>Curtain</t>
+          <t>Smoke alarm</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -17780,7 +17811,7 @@
     <row r="115" ht="20" customHeight="1">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>Schüco Polymer Technologies KG</t>
+          <t>Savant</t>
         </is>
       </c>
       <c r="B115" s="6" t="n">
@@ -17788,12 +17819,12 @@
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Curtain</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
@@ -17805,7 +17836,7 @@
     <row r="116" ht="20" customHeight="1">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Secuyou</t>
+          <t>Schüco Polymer Technologies KG</t>
         </is>
       </c>
       <c r="B116" s="4" t="n">
@@ -17813,12 +17844,12 @@
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -17830,7 +17861,7 @@
     <row r="117" ht="20" customHeight="1">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>Shenzhen BOFU smart.co.,ltd</t>
+          <t>Secuyou</t>
         </is>
       </c>
       <c r="B117" s="6" t="n">
@@ -17838,12 +17869,12 @@
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>Blind</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
@@ -17855,7 +17886,7 @@
     <row r="118" ht="20" customHeight="1">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Shenzhen Conex Intelligent Technology Co.,Ltd</t>
+          <t>Shenzhen BOFU smart.co.,ltd</t>
         </is>
       </c>
       <c r="B118" s="4" t="n">
@@ -17863,12 +17894,12 @@
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Blind</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -17880,7 +17911,7 @@
     <row r="119" ht="20" customHeight="1">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>Signify Netherlands B.V.</t>
+          <t>Shenzhen Conex Intelligent Technology Co.,Ltd</t>
         </is>
       </c>
       <c r="B119" s="6" t="n">
@@ -17888,12 +17919,12 @@
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>Bulb</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
@@ -17905,7 +17936,7 @@
     <row r="120" ht="20" customHeight="1">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Siterwell Electronics Co., Limited</t>
+          <t>Signify Netherlands B.V.</t>
         </is>
       </c>
       <c r="B120" s="4" t="n">
@@ -17913,12 +17944,12 @@
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>Smoke alarm</t>
+          <t>Bulb</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -17930,7 +17961,7 @@
     <row r="121" ht="20" customHeight="1">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>SmartWings Home LLC</t>
+          <t>Siterwell Electronics Co., Limited</t>
         </is>
       </c>
       <c r="B121" s="6" t="n">
@@ -17938,12 +17969,12 @@
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>Blind</t>
+          <t>Smoke alarm</t>
         </is>
       </c>
       <c r="E121" s="7" t="inlineStr">
@@ -17955,7 +17986,7 @@
     <row r="122" ht="20" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>TETNET OÜ</t>
+          <t>SmartWings Home LLC</t>
         </is>
       </c>
       <c r="B122" s="4" t="n">
@@ -17968,7 +17999,7 @@
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>Window lock</t>
+          <t>Blind</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -17980,7 +18011,7 @@
     <row r="123" ht="20" customHeight="1">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>Tedee Sp. z o.o.</t>
+          <t>TETNET OÜ</t>
         </is>
       </c>
       <c r="B123" s="6" t="n">
@@ -17988,12 +18019,12 @@
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Window lock</t>
         </is>
       </c>
       <c r="E123" s="7" t="inlineStr">
@@ -18005,7 +18036,7 @@
     <row r="124" ht="20" customHeight="1">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Vitrumshade LLC</t>
+          <t>Tedee Sp. z o.o.</t>
         </is>
       </c>
       <c r="B124" s="4" t="n">
@@ -18013,12 +18044,12 @@
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>Blind</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -18030,7 +18061,7 @@
     <row r="125" ht="20" customHeight="1">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>WINTECKOREA INC</t>
+          <t>Vitrumshade LLC</t>
         </is>
       </c>
       <c r="B125" s="6" t="n">
@@ -18055,7 +18086,7 @@
     <row r="126" ht="20" customHeight="1">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>WNC Corporation</t>
+          <t>WINTECKOREA INC</t>
         </is>
       </c>
       <c r="B126" s="4" t="n">
@@ -18063,12 +18094,12 @@
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Blind</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -18080,7 +18111,7 @@
     <row r="127" ht="20" customHeight="1">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>WideSky.cloud Pty. Ltd</t>
+          <t>WNC Corporation</t>
         </is>
       </c>
       <c r="B127" s="6" t="n">
@@ -18088,12 +18119,12 @@
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr">
@@ -18105,7 +18136,7 @@
     <row r="128" ht="20" customHeight="1">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Xiaomi Communications Co., Ltd.</t>
+          <t>WideSky.cloud Pty. Ltd</t>
         </is>
       </c>
       <c r="B128" s="4" t="n">
@@ -18113,12 +18144,12 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -18130,7 +18161,7 @@
     <row r="129" ht="20" customHeight="1">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>Zhejiang General light Curtain Co., Ltd.</t>
+          <t>Xiaomi Communications Co., Ltd.</t>
         </is>
       </c>
       <c r="B129" s="6" t="n">
@@ -18138,12 +18169,12 @@
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>Blind</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="E129" s="7" t="inlineStr">
@@ -18155,7 +18186,7 @@
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>Zhejiang Jiecang Linear Motion Technology Co.,Ltd</t>
+          <t>Zhejiang General light Curtain Co., Ltd.</t>
         </is>
       </c>
       <c r="B130" s="4" t="n">
@@ -18180,7 +18211,7 @@
     <row r="131" ht="20" customHeight="1">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>Zhejiang Moorgen Group Co., Ltd.</t>
+          <t>Zhejiang Jiecang Linear Motion Technology Co.,Ltd</t>
         </is>
       </c>
       <c r="B131" s="6" t="n">
@@ -18188,22 +18219,47 @@
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
+          <t>Window covering</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>Blind</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>Built on Thread</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>Zhejiang Moorgen Group Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
           <t>Lighting</t>
         </is>
       </c>
-      <c r="D131" s="7" t="inlineStr">
+      <c r="D132" s="5" t="inlineStr">
         <is>
           <t>Light</t>
         </is>
       </c>
-      <c r="E131" s="7" t="inlineStr">
+      <c r="E132" s="5" t="inlineStr">
         <is>
           <t>Built on Thread</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E131"/>
+  <autoFilter ref="A3:E132"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -18310,7 +18366,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -18382,7 +18438,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -18438,7 +18494,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -18528,7 +18584,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="24">
